--- a/wiki/sources/analyses/20231103-TYNDP2024-GRID.xlsx
+++ b/wiki/sources/analyses/20231103-TYNDP2024-GRID.xlsx
@@ -1692,7 +1692,7 @@
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1812,6 +1812,12 @@
       <name val="Calibri"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1878,7 +1884,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1940,6 +1946,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2052,9 +2062,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
-      <xdr:colOff>132840</xdr:colOff>
+      <xdr:colOff>132120</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>142200</xdr:rowOff>
+      <xdr:rowOff>141480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2064,7 +2074,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="231840" y="181080"/>
-          <a:ext cx="13965480" cy="9552960"/>
+          <a:ext cx="13964760" cy="9552240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2162,18 +2172,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>In March -April 2023 ENTSO-E collected projects to be included in reference grid for TYNDP 2024 Scenario </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>Building process purposes.</a:t>
+            <a:t>In March -April 2023 ENTSO-E collected projects to be included in reference grid for TYNDP 2024 Scenario Building process purposes.</a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2208,29 +2207,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>TYNDP 2022 Project Promoters (both TSOs and third parties) were requested to fill/update the technical </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>information regarding the investments included in their promoted projects, provide the project dNTC </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>impact and point.</a:t>
+            <a:t>TYNDP 2022 Project Promoters (both TSOs and third parties) were requested to fill/update the technical information regarding the investments included in their promoted projects, provide the project dNTC impact and point.</a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2265,29 +2242,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>Justification for the given selection according to the 4th CBA Guidelines had to be provided accordingly: </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>https://eepublicdownloads.blob.core.windows.net/public-cdn-container/tyndp-documents/CBA/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>CBA4/221215_CBA4-Guideline_v1.0_for-public-consultation.pdf </a:t>
+            <a:t>Justification for the given selection according to the 4th CBA Guidelines had to be provided accordingly: https://eepublicdownloads.blob.core.windows.net/public-cdn-container/tyndp-documents/CBA/CBA4/221215_CBA4-Guideline_v1.0_for-public-consultation.pdf </a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2322,51 +2277,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>Based on the guidance given within the 4th CBA Guidelines the reference grid for the 2030 horizon, which </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>corresponds to the mid-term horizon, is based on criteria a) and b) as defined within the 4th CBA </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>Guideline. This means that only projects which, at their time of submission to the TYNDP, are in the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>construction phase or those which have successfully completed the environmental impact assessment </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>could be part of the 2030 reference grid.</a:t>
+            <a:t>Based on the guidance given within the 4th CBA Guidelines the reference grid for the 2030 horizon, which corresponds to the mid-term horizon, is based on criteria a) and b) as defined within the 4th CBA Guideline. This means that only projects which, at their time of submission to the TYNDP, are in the construction phase or those which have successfully completed the environmental impact assessment could be part of the 2030 reference grid.</a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2401,62 +2312,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>In addition to the above given maturity criteria, a cut-off for the commissioning years has been set. This </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>choice deals with the uncertainties in the planning and construction, ensuring that only projects with a </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>strong chance of being commissioned at the dates of the respective scenarios are part of the reference </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>grid. The cut-off has been set to 31 December 2030 for the mid-term horizon (2030) and 31 December </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>2035 for the long-term horizon (2040), excluding all projects with planned commissioning dates later than </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>these cut-offs. </a:t>
+            <a:t>In addition to the above given maturity criteria, a cut-off for the commissioning years has been set. This choice deals with the uncertainties in the planning and construction, ensuring that only projects with a strong chance of being commissioned at the dates of the respective scenarios are part of the reference grid. The cut-off has been set to 31 December 2030 for the mid-term horizon (2030) and 31 December 2035 for the long-term horizon (2040), excluding all projects with planned commissioning dates later than these cut-offs. </a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2514,51 +2370,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>This file gathers the hydrogen reference grid, that is, all cross-border transmission (or, interconnector) </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>capacities across Europe, according to the data that member TSOs have for 2030. The aforementioned year </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>is the only one for which a reference grid is provided, as 2030 is the starting point for the DE/GA scenarios. </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>After 2030, investment can happen in transmission candidate projects, which are gathered in a separate </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>file.</a:t>
+            <a:t>This file gathers the hydrogen reference grid, that is, all cross-border transmission (or, interconnector) capacities across Europe, according to the data that member TSOs have for 2030. The aforementioned year is the only one for which a reference grid is provided, as 2030 is the starting point for the DE/GA scenarios. After 2030, investment can happen in transmission candidate projects, which are gathered in a separate file.</a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2616,18 +2428,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>- Border --- the border on which the interconnector is found (note that the nodes linked by interconnector </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>keep the ISO2 naming convention)</a:t>
+            <a:t>- Border --- the border on which the interconnector is found (note that the nodes linked by interconnector keep the ISO2 naming convention)</a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2673,18 +2474,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>- Summary Direction 2 --- capacity of interconnector (GW) in the direction opposite to the one found in the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>index, e.g., DE to AT</a:t>
+            <a:t>- Summary Direction 2 --- capacity of interconnector (GW) in the direction opposite to the one found in the index, e.g., DE to AT</a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2835,40 +2625,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>In the first step the existing projects from the already published TYNDP list were used with their economic </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>parameters (CAPEX, OPEX, transfer capacity Impact). Those candidates constitute very reliable base for the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>system needs studies together with scenario building process, as these projects were analyzed within the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>TYNDP CBA phase and were consulted with ACER and European NRAs. </a:t>
+            <a:t>In the first step the existing projects from the already published TYNDP list were used with their economic parameters (CAPEX, OPEX, transfer capacity Impact). Those candidates constitute very reliable base for the system needs studies together with scenario building process, as these projects were analyzed within the TYNDP CBA phase and were consulted with ACER and European NRAs. </a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -2903,73 +2660,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>In the second phase, project promoters from the last already published TYNDP cycle were given an </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>opportunity to submit new candidates. Most of such candidates were submitted by ENTSO-E TSOs with </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>clear distinguished economic parameters. CAPEX for such projects also had to include the costs of the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>internal reinforcements that are accompanying the project implementation. As the important step, TSOs </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>had opportunity to add additional costs associated with internal reinforcements for the projects that were </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>submitted by 3rd party organizations. This step is very logical, considering the deep knowledge of the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>national network by given TSOs. </a:t>
+            <a:t>In the second phase, project promoters from the last already published TYNDP cycle were given an opportunity to submit new candidates. Most of such candidates were submitted by ENTSO-E TSOs with clear distinguished economic parameters. CAPEX for such projects also had to include the costs of the internal reinforcements that are accompanying the project implementation. As the important step, TSOs had opportunity to add additional costs associated with internal reinforcements for the projects that were submitted by 3rd party organizations. This step is very logical, considering the deep knowledge of the national network by given TSOs. </a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -3004,51 +2695,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>It is important to note that all the conceptual projects (not yet submitted in ENTSO-E TYNDP cycle) are </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>those candidates for which TSOs were already investigating the possibility of potential new </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>interconnection, therefore, economic parameters of such project candidates could be to some degree </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>uncertain but very probable and technically justifiable. In some cases, even preliminary technical studies </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>were performed to analyze potential new connections. </a:t>
+            <a:t>It is important to note that all the conceptual projects (not yet submitted in ENTSO-E TYNDP cycle) are those candidates for which TSOs were already investigating the possibility of potential new interconnection, therefore, economic parameters of such project candidates could be to some degree uncertain but very probable and technically justifiable. In some cases, even preliminary technical studies were performed to analyze potential new connections. </a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -3128,62 +2775,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>In the TYNDP 2022, each target year (2030, 2040, 2050) has 2 infrastructure levels available a "low </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>infrastructure level" and a "high infrastructure level". The "Low infrastrucuture level" is a collection of </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>projects submitted to the first hydrogen TYNDP in 2022. An approach based on project status (as was used </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>for the methane TYNDP) is not a meaningful KPI when developing infrastructure from inauguration. the </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>"high infrastructure level" includes additional cross border capacities submitted by TSOs to ENTSOG's H2 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>Taskforce. </a:t>
+            <a:t>In the TYNDP 2022, each target year (2030, 2040, 2050) has 2 infrastructure levels available a "low infrastructure level" and a "high infrastructure level". The "Low infrastrucuture level" is a collection of projects submitted to the first hydrogen TYNDP in 2022. An approach based on project status (as was used for the methane TYNDP) is not a meaningful KPI when developing infrastructure from inauguration. the "high infrastructure level" includes additional cross border capacities submitted by TSOs to ENTSOG's H2 Taskforce. </a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -3218,18 +2810,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>The hydrogen candidate projects used are based on the difference in pipeline capacity between "low </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>infrastructure level" and "high infrastructure level", for each target year. </a:t>
+            <a:t>The hydrogen candidate projects used are based on the difference in pipeline capacity between "low infrastructure level" and "high infrastructure level", for each target year. </a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -3264,84 +2845,7 @@
               <a:uFillTx/>
               <a:latin typeface="Calibri"/>
             </a:rPr>
-            <a:t>Infrastructure costs must then be considered for the expansion of hydrogen pipeline. As there is almost no </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>real world data for this, the cost are based on external studies. The main study used is the 'European </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>Hydrogen Backbone" studies. The methodology followed based on this study is, CAPEX cost are split </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>between repurposed and new hydrogen pipeline with a split of 60% to 40% respectively. A distance must </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>also be considered, in this case either the default distance of 30% of the distance from capital to capital is </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>used, referencing a distance related dataset from ewi study on the cost of H2 imports to the EU, or a </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>different distance provided by the TSO to include a country specific viw that is not captured by the general </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="Calibri"/>
-            </a:rPr>
-            <a:t>methodology.</a:t>
+            <a:t>Infrastructure costs must then be considered for the expansion of hydrogen pipeline. As there is almost no real world data for this, the cost are based on external studies. The main study used is the 'European Hydrogen Backbone" studies. The methodology followed based on this study is, CAPEX cost are split between repurposed and new hydrogen pipeline with a split of 60% to 40% respectively. A distance must also be considered, in this case either the default distance of 30% of the distance from capital to capital is used, referencing a distance related dataset from ewi study on the cost of H2 imports to the EU, or a different distance provided by the TSO to include a country specific viw that is not captured by the general methodology.</a:t>
           </a:r>
           <a:endParaRPr lang="en-DK" sz="1100" b="0" u="none" strike="noStrike">
             <a:effectLst/>
@@ -3367,9 +2871,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>127080</xdr:colOff>
+      <xdr:colOff>126360</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>18360</xdr:rowOff>
+      <xdr:rowOff>17640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3379,7 +2883,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10833840" y="343080"/>
-          <a:ext cx="5775480" cy="3294720"/>
+          <a:ext cx="5774760" cy="3294000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3604,9 +3108,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>466200</xdr:colOff>
+      <xdr:colOff>465480</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>56520</xdr:rowOff>
+      <xdr:rowOff>55800</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3616,7 +3120,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5157360" y="238320"/>
-          <a:ext cx="5420520" cy="3075840"/>
+          <a:ext cx="5419800" cy="3075120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3841,9 +3345,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>138960</xdr:colOff>
+      <xdr:colOff>138240</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>34200</xdr:rowOff>
+      <xdr:rowOff>33480</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3853,7 +3357,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9137520" y="504720"/>
-          <a:ext cx="6360840" cy="6406560"/>
+          <a:ext cx="6360120" cy="6405840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4525,9 +4029,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>319680</xdr:colOff>
+      <xdr:colOff>318960</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>150120</xdr:rowOff>
+      <xdr:rowOff>149400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -4537,7 +4041,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6621840" y="133200"/>
-          <a:ext cx="6395400" cy="5084280"/>
+          <a:ext cx="6394680" cy="5083560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -17387,7 +16891,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E486"/>
+  <dimension ref="A1:H486"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17409,11 +16913,11 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A2,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A2,FIND("-",'1. Elec Ref Grid'!A2)-1)</f>
         <v>AL00</v>
       </c>
       <c r="B2" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A2,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A2,LEN('1. Elec Ref Grid'!A2)-FIND("-",'1. Elec Ref Grid'!A2))</f>
         <v>GR00</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -17429,11 +16933,11 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A3,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A3,FIND("-",'1. Elec Ref Grid'!A3)-1)</f>
         <v>AL00</v>
       </c>
       <c r="B3" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A3,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A3,LEN('1. Elec Ref Grid'!A3)-FIND("-",'1. Elec Ref Grid'!A3))</f>
         <v>ME00</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -17449,11 +16953,11 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A4,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A4,FIND("-",'1. Elec Ref Grid'!A4)-1)</f>
         <v>AL00</v>
       </c>
       <c r="B4" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A4,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A4,LEN('1. Elec Ref Grid'!A4)-FIND("-",'1. Elec Ref Grid'!A4))</f>
         <v>MK00</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -17469,11 +16973,11 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A5,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A5,FIND("-",'1. Elec Ref Grid'!A5)-1)</f>
         <v>AL00</v>
       </c>
       <c r="B5" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A5,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A5,LEN('1. Elec Ref Grid'!A5)-FIND("-",'1. Elec Ref Grid'!A5))</f>
         <v>RS00</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -17489,11 +16993,11 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A6,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A6,FIND("-",'1. Elec Ref Grid'!A6)-1)</f>
         <v>AT00</v>
       </c>
       <c r="B6" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A6,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A6,LEN('1. Elec Ref Grid'!A6)-FIND("-",'1. Elec Ref Grid'!A6))</f>
         <v>CH00</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -17509,11 +17013,11 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A7,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A7,FIND("-",'1. Elec Ref Grid'!A7)-1)</f>
         <v>AT00</v>
       </c>
       <c r="B7" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A7,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A7,LEN('1. Elec Ref Grid'!A7)-FIND("-",'1. Elec Ref Grid'!A7))</f>
         <v>CZ00</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -17529,11 +17033,11 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A8,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A8,FIND("-",'1. Elec Ref Grid'!A8)-1)</f>
         <v>AT00</v>
       </c>
       <c r="B8" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A8,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A8,LEN('1. Elec Ref Grid'!A8)-FIND("-",'1. Elec Ref Grid'!A8))</f>
         <v>DE00</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -17549,11 +17053,11 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A9,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A9,FIND("-",'1. Elec Ref Grid'!A9)-1)</f>
         <v>AT00</v>
       </c>
       <c r="B9" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A9,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A9,LEN('1. Elec Ref Grid'!A9)-FIND("-",'1. Elec Ref Grid'!A9))</f>
         <v>HU00</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -17569,11 +17073,11 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A10,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A10,FIND("-",'1. Elec Ref Grid'!A10)-1)</f>
         <v>AT00</v>
       </c>
       <c r="B10" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A10,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A10,LEN('1. Elec Ref Grid'!A10)-FIND("-",'1. Elec Ref Grid'!A10))</f>
         <v>ITN1</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -17589,11 +17093,11 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A11,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A11,FIND("-",'1. Elec Ref Grid'!A11)-1)</f>
         <v>AT00</v>
       </c>
       <c r="B11" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A11,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A11,LEN('1. Elec Ref Grid'!A11)-FIND("-",'1. Elec Ref Grid'!A11))</f>
         <v>SI00</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -17609,11 +17113,11 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A12,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A12,FIND("-",'1. Elec Ref Grid'!A12)-1)</f>
         <v>AT00</v>
       </c>
       <c r="B12" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A12,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A12,LEN('1. Elec Ref Grid'!A12)-FIND("-",'1. Elec Ref Grid'!A12))</f>
         <v>SK00</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -17629,11 +17133,11 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A13,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A13,FIND("-",'1. Elec Ref Grid'!A13)-1)</f>
         <v>BA00</v>
       </c>
       <c r="B13" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A13,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A13,LEN('1. Elec Ref Grid'!A13)-FIND("-",'1. Elec Ref Grid'!A13))</f>
         <v>HR00</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -17649,11 +17153,11 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A14,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A14,FIND("-",'1. Elec Ref Grid'!A14)-1)</f>
         <v>BA00</v>
       </c>
       <c r="B14" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A14,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A14,LEN('1. Elec Ref Grid'!A14)-FIND("-",'1. Elec Ref Grid'!A14))</f>
         <v>ME00</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -17669,11 +17173,11 @@
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A15,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A15,FIND("-",'1. Elec Ref Grid'!A15)-1)</f>
         <v>BA00</v>
       </c>
       <c r="B15" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A15,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A15,LEN('1. Elec Ref Grid'!A15)-FIND("-",'1. Elec Ref Grid'!A15))</f>
         <v>RS00</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -17689,11 +17193,11 @@
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A16,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A16,FIND("-",'1. Elec Ref Grid'!A16)-1)</f>
         <v>BE00</v>
       </c>
       <c r="B16" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A16,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A16,LEN('1. Elec Ref Grid'!A16)-FIND("-",'1. Elec Ref Grid'!A16))</f>
         <v>DE00</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -17709,11 +17213,11 @@
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A17,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A17,FIND("-",'1. Elec Ref Grid'!A17)-1)</f>
         <v>BE00</v>
       </c>
       <c r="B17" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A17,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A17,LEN('1. Elec Ref Grid'!A17)-FIND("-",'1. Elec Ref Grid'!A17))</f>
         <v>FR00</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -17729,11 +17233,11 @@
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A18,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A18,FIND("-",'1. Elec Ref Grid'!A18)-1)</f>
         <v>BE00</v>
       </c>
       <c r="B18" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A18,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A18,LEN('1. Elec Ref Grid'!A18)-FIND("-",'1. Elec Ref Grid'!A18))</f>
         <v>LUB1</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -17749,11 +17253,11 @@
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A19,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A19,FIND("-",'1. Elec Ref Grid'!A19)-1)</f>
         <v>BE00</v>
       </c>
       <c r="B19" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A19,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A19,LEN('1. Elec Ref Grid'!A19)-FIND("-",'1. Elec Ref Grid'!A19))</f>
         <v>LUG1</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -17769,11 +17273,11 @@
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A20,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A20,FIND("-",'1. Elec Ref Grid'!A20)-1)</f>
         <v>BE00</v>
       </c>
       <c r="B20" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A20,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A20,LEN('1. Elec Ref Grid'!A20)-FIND("-",'1. Elec Ref Grid'!A20))</f>
         <v>NL00</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -17789,11 +17293,11 @@
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A21,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A21,FIND("-",'1. Elec Ref Grid'!A21)-1)</f>
         <v>BE00</v>
       </c>
       <c r="B21" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A21,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A21,LEN('1. Elec Ref Grid'!A21)-FIND("-",'1. Elec Ref Grid'!A21))</f>
         <v>UK00</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -17809,11 +17313,11 @@
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A22,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A22,FIND("-",'1. Elec Ref Grid'!A22)-1)</f>
         <v>BG00</v>
       </c>
       <c r="B22" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A22,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A22,LEN('1. Elec Ref Grid'!A22)-FIND("-",'1. Elec Ref Grid'!A22))</f>
         <v>GR00</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -17829,11 +17333,11 @@
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A23,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A23,FIND("-",'1. Elec Ref Grid'!A23)-1)</f>
         <v>BG00</v>
       </c>
       <c r="B23" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A23,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A23,LEN('1. Elec Ref Grid'!A23)-FIND("-",'1. Elec Ref Grid'!A23))</f>
         <v>MK00</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -17849,11 +17353,11 @@
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A24,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A24,FIND("-",'1. Elec Ref Grid'!A24)-1)</f>
         <v>BG00</v>
       </c>
       <c r="B24" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A24,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A24,LEN('1. Elec Ref Grid'!A24)-FIND("-",'1. Elec Ref Grid'!A24))</f>
         <v>RO00</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -17869,11 +17373,11 @@
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A25,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A25,FIND("-",'1. Elec Ref Grid'!A25)-1)</f>
         <v>BG00</v>
       </c>
       <c r="B25" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A25,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A25,LEN('1. Elec Ref Grid'!A25)-FIND("-",'1. Elec Ref Grid'!A25))</f>
         <v>RS00</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -17889,11 +17393,11 @@
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A26,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A26,FIND("-",'1. Elec Ref Grid'!A26)-1)</f>
         <v>BG00</v>
       </c>
       <c r="B26" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A26,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A26,LEN('1. Elec Ref Grid'!A26)-FIND("-",'1. Elec Ref Grid'!A26))</f>
         <v>TR00</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -17909,11 +17413,11 @@
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A27,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A27,FIND("-",'1. Elec Ref Grid'!A27)-1)</f>
         <v>CH00</v>
       </c>
       <c r="B27" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A27,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A27,LEN('1. Elec Ref Grid'!A27)-FIND("-",'1. Elec Ref Grid'!A27))</f>
         <v>DE00</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -17929,11 +17433,11 @@
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A28,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A28,FIND("-",'1. Elec Ref Grid'!A28)-1)</f>
         <v>CH00</v>
       </c>
       <c r="B28" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A28,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A28,LEN('1. Elec Ref Grid'!A28)-FIND("-",'1. Elec Ref Grid'!A28))</f>
         <v>FR00</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -17949,11 +17453,11 @@
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A29,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A29,FIND("-",'1. Elec Ref Grid'!A29)-1)</f>
         <v>CH00</v>
       </c>
       <c r="B29" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A29,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A29,LEN('1. Elec Ref Grid'!A29)-FIND("-",'1. Elec Ref Grid'!A29))</f>
         <v>ITN1</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -17969,11 +17473,11 @@
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A30,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A30,FIND("-",'1. Elec Ref Grid'!A30)-1)</f>
         <v>CY00</v>
       </c>
       <c r="B30" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A30,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A30,LEN('1. Elec Ref Grid'!A30)-FIND("-",'1. Elec Ref Grid'!A30))</f>
         <v>EG00</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -17989,11 +17493,11 @@
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A31,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A31,FIND("-",'1. Elec Ref Grid'!A31)-1)</f>
         <v>CY00</v>
       </c>
       <c r="B31" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A31,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A31,LEN('1. Elec Ref Grid'!A31)-FIND("-",'1. Elec Ref Grid'!A31))</f>
         <v>GR03</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -18009,11 +17513,11 @@
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A32,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A32,FIND("-",'1. Elec Ref Grid'!A32)-1)</f>
         <v>CY00</v>
       </c>
       <c r="B32" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A32,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A32,LEN('1. Elec Ref Grid'!A32)-FIND("-",'1. Elec Ref Grid'!A32))</f>
         <v>IL00</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -18029,11 +17533,11 @@
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A33,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A33,FIND("-",'1. Elec Ref Grid'!A33)-1)</f>
         <v>CZ00</v>
       </c>
       <c r="B33" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A33,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A33,LEN('1. Elec Ref Grid'!A33)-FIND("-",'1. Elec Ref Grid'!A33))</f>
         <v>DE00</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -18049,12 +17553,12 @@
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A34,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A34,FIND("-",'1. Elec Ref Grid'!A34)-1)</f>
         <v>CZ00</v>
       </c>
       <c r="B34" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A34,4)</f>
-        <v>L00I</v>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A34,LEN('1. Elec Ref Grid'!A34)-FIND("-",'1. Elec Ref Grid'!A34))</f>
+        <v>PL00I</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>547</v>
@@ -18069,11 +17573,11 @@
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A35,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A35,FIND("-",'1. Elec Ref Grid'!A35)-1)</f>
         <v>CZ00</v>
       </c>
       <c r="B35" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A35,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A35,LEN('1. Elec Ref Grid'!A35)-FIND("-",'1. Elec Ref Grid'!A35))</f>
         <v>SK00</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -18089,11 +17593,11 @@
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A36,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A36,FIND("-",'1. Elec Ref Grid'!A36)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B36" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A36,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A36,LEN('1. Elec Ref Grid'!A36)-FIND("-",'1. Elec Ref Grid'!A36))</f>
         <v>DEKF</v>
       </c>
       <c r="C36" s="1" t="s">
@@ -18109,11 +17613,11 @@
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A37,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A37,FIND("-",'1. Elec Ref Grid'!A37)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B37" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A37,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A37,LEN('1. Elec Ref Grid'!A37)-FIND("-",'1. Elec Ref Grid'!A37))</f>
         <v>DKE1</v>
       </c>
       <c r="C37" s="1" t="s">
@@ -18129,11 +17633,11 @@
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A38,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A38,FIND("-",'1. Elec Ref Grid'!A38)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B38" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A38,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A38,LEN('1. Elec Ref Grid'!A38)-FIND("-",'1. Elec Ref Grid'!A38))</f>
         <v>DKW1</v>
       </c>
       <c r="C38" s="1" t="s">
@@ -18149,11 +17653,11 @@
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A39,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A39,FIND("-",'1. Elec Ref Grid'!A39)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B39" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A39,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A39,LEN('1. Elec Ref Grid'!A39)-FIND("-",'1. Elec Ref Grid'!A39))</f>
         <v>FR00</v>
       </c>
       <c r="C39" s="1" t="s">
@@ -18169,11 +17673,11 @@
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A40,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A40,FIND("-",'1. Elec Ref Grid'!A40)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B40" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A40,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A40,LEN('1. Elec Ref Grid'!A40)-FIND("-",'1. Elec Ref Grid'!A40))</f>
         <v>LUG1</v>
       </c>
       <c r="C40" s="1" t="s">
@@ -18189,11 +17693,11 @@
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A41,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A41,FIND("-",'1. Elec Ref Grid'!A41)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B41" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A41,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A41,LEN('1. Elec Ref Grid'!A41)-FIND("-",'1. Elec Ref Grid'!A41))</f>
         <v>LUV1</v>
       </c>
       <c r="C41" s="1" t="s">
@@ -18209,11 +17713,11 @@
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A42,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A42,FIND("-",'1. Elec Ref Grid'!A42)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B42" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A42,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A42,LEN('1. Elec Ref Grid'!A42)-FIND("-",'1. Elec Ref Grid'!A42))</f>
         <v>NL00</v>
       </c>
       <c r="C42" s="1" t="s">
@@ -18229,11 +17733,11 @@
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A43,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A43,FIND("-",'1. Elec Ref Grid'!A43)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B43" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A43,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A43,LEN('1. Elec Ref Grid'!A43)-FIND("-",'1. Elec Ref Grid'!A43))</f>
         <v>NOS0</v>
       </c>
       <c r="C43" s="1" t="s">
@@ -18249,12 +17753,12 @@
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A44,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A44,FIND("-",'1. Elec Ref Grid'!A44)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B44" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A44,4)</f>
-        <v>L00I</v>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A44,LEN('1. Elec Ref Grid'!A44)-FIND("-",'1. Elec Ref Grid'!A44))</f>
+        <v>PL00I</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>547</v>
@@ -18269,11 +17773,11 @@
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A45,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A45,FIND("-",'1. Elec Ref Grid'!A45)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B45" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A45,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A45,LEN('1. Elec Ref Grid'!A45)-FIND("-",'1. Elec Ref Grid'!A45))</f>
         <v>SE04</v>
       </c>
       <c r="C45" s="1" t="s">
@@ -18289,11 +17793,11 @@
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A46,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A46,FIND("-",'1. Elec Ref Grid'!A46)-1)</f>
         <v>DE00</v>
       </c>
       <c r="B46" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A46,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A46,LEN('1. Elec Ref Grid'!A46)-FIND("-",'1. Elec Ref Grid'!A46))</f>
         <v>UK00</v>
       </c>
       <c r="C46" s="1" t="s">
@@ -18309,11 +17813,11 @@
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A47,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A47,FIND("-",'1. Elec Ref Grid'!A47)-1)</f>
         <v>DEKF</v>
       </c>
       <c r="B47" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A47,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A47,LEN('1. Elec Ref Grid'!A47)-FIND("-",'1. Elec Ref Grid'!A47))</f>
         <v>DKKF</v>
       </c>
       <c r="C47" s="1" t="s">
@@ -18329,11 +17833,11 @@
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A48,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A48,FIND("-",'1. Elec Ref Grid'!A48)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="B48" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A48,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A48,LEN('1. Elec Ref Grid'!A48)-FIND("-",'1. Elec Ref Grid'!A48))</f>
         <v>DKKF</v>
       </c>
       <c r="C48" s="1" t="s">
@@ -18349,11 +17853,11 @@
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A49,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A49,FIND("-",'1. Elec Ref Grid'!A49)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="B49" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A49,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A49,LEN('1. Elec Ref Grid'!A49)-FIND("-",'1. Elec Ref Grid'!A49))</f>
         <v>DKW1</v>
       </c>
       <c r="C49" s="1" t="s">
@@ -18369,11 +17873,11 @@
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A50,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A50,FIND("-",'1. Elec Ref Grid'!A50)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="B50" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A50,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A50,LEN('1. Elec Ref Grid'!A50)-FIND("-",'1. Elec Ref Grid'!A50))</f>
         <v>PL00</v>
       </c>
       <c r="C50" s="1" t="s">
@@ -18389,11 +17893,11 @@
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A51,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A51,FIND("-",'1. Elec Ref Grid'!A51)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="B51" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A51,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A51,LEN('1. Elec Ref Grid'!A51)-FIND("-",'1. Elec Ref Grid'!A51))</f>
         <v>SE04</v>
       </c>
       <c r="C51" s="1" t="s">
@@ -18409,11 +17913,11 @@
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A52,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A52,FIND("-",'1. Elec Ref Grid'!A52)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="B52" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A52,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A52,LEN('1. Elec Ref Grid'!A52)-FIND("-",'1. Elec Ref Grid'!A52))</f>
         <v>NL00</v>
       </c>
       <c r="C52" s="1" t="s">
@@ -18429,11 +17933,11 @@
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A53,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A53,FIND("-",'1. Elec Ref Grid'!A53)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="B53" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A53,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A53,LEN('1. Elec Ref Grid'!A53)-FIND("-",'1. Elec Ref Grid'!A53))</f>
         <v>NOS0</v>
       </c>
       <c r="C53" s="1" t="s">
@@ -18449,11 +17953,11 @@
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A54,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A54,FIND("-",'1. Elec Ref Grid'!A54)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="B54" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A54,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A54,LEN('1. Elec Ref Grid'!A54)-FIND("-",'1. Elec Ref Grid'!A54))</f>
         <v>SE03</v>
       </c>
       <c r="C54" s="1" t="s">
@@ -18469,11 +17973,11 @@
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A55,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A55,FIND("-",'1. Elec Ref Grid'!A55)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="B55" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A55,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A55,LEN('1. Elec Ref Grid'!A55)-FIND("-",'1. Elec Ref Grid'!A55))</f>
         <v>UK00</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -18489,11 +17993,11 @@
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A56,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A56,FIND("-",'1. Elec Ref Grid'!A56)-1)</f>
         <v>DZ00</v>
       </c>
       <c r="B56" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A56,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A56,LEN('1. Elec Ref Grid'!A56)-FIND("-",'1. Elec Ref Grid'!A56))</f>
         <v>MA00</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -18509,11 +18013,11 @@
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A57,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A57,FIND("-",'1. Elec Ref Grid'!A57)-1)</f>
         <v>DZ00</v>
       </c>
       <c r="B57" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A57,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A57,LEN('1. Elec Ref Grid'!A57)-FIND("-",'1. Elec Ref Grid'!A57))</f>
         <v>TN00</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -18529,11 +18033,11 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A58,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A58,FIND("-",'1. Elec Ref Grid'!A58)-1)</f>
         <v>EE00</v>
       </c>
       <c r="B58" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A58,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A58,LEN('1. Elec Ref Grid'!A58)-FIND("-",'1. Elec Ref Grid'!A58))</f>
         <v>FI00</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -18549,11 +18053,11 @@
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A59,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A59,FIND("-",'1. Elec Ref Grid'!A59)-1)</f>
         <v>EE00</v>
       </c>
       <c r="B59" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A59,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A59,LEN('1. Elec Ref Grid'!A59)-FIND("-",'1. Elec Ref Grid'!A59))</f>
         <v>LV00</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -18569,11 +18073,11 @@
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A60,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A60,FIND("-",'1. Elec Ref Grid'!A60)-1)</f>
         <v>EG00</v>
       </c>
       <c r="B60" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A60,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A60,LEN('1. Elec Ref Grid'!A60)-FIND("-",'1. Elec Ref Grid'!A60))</f>
         <v>GR00</v>
       </c>
       <c r="C60" s="1" t="s">
@@ -18589,11 +18093,11 @@
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A61,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A61,FIND("-",'1. Elec Ref Grid'!A61)-1)</f>
         <v>EG00</v>
       </c>
       <c r="B61" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A61,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A61,LEN('1. Elec Ref Grid'!A61)-FIND("-",'1. Elec Ref Grid'!A61))</f>
         <v>LY00</v>
       </c>
       <c r="C61" s="1" t="s">
@@ -18609,11 +18113,11 @@
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A62,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A62,FIND("-",'1. Elec Ref Grid'!A62)-1)</f>
         <v>ES00</v>
       </c>
       <c r="B62" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A62,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A62,LEN('1. Elec Ref Grid'!A62)-FIND("-",'1. Elec Ref Grid'!A62))</f>
         <v>FR00</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -18629,11 +18133,11 @@
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A63,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A63,FIND("-",'1. Elec Ref Grid'!A63)-1)</f>
         <v>ES00</v>
       </c>
       <c r="B63" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A63,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A63,LEN('1. Elec Ref Grid'!A63)-FIND("-",'1. Elec Ref Grid'!A63))</f>
         <v>MA00</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -18649,11 +18153,11 @@
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A64,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A64,FIND("-",'1. Elec Ref Grid'!A64)-1)</f>
         <v>ES00</v>
       </c>
       <c r="B64" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A64,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A64,LEN('1. Elec Ref Grid'!A64)-FIND("-",'1. Elec Ref Grid'!A64))</f>
         <v>PT00</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -18669,11 +18173,11 @@
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A65,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A65,FIND("-",'1. Elec Ref Grid'!A65)-1)</f>
         <v>FI00</v>
       </c>
       <c r="B65" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A65,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A65,LEN('1. Elec Ref Grid'!A65)-FIND("-",'1. Elec Ref Grid'!A65))</f>
         <v>NON1</v>
       </c>
       <c r="C65" s="1" t="s">
@@ -18689,11 +18193,11 @@
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A66,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A66,FIND("-",'1. Elec Ref Grid'!A66)-1)</f>
         <v>FI00</v>
       </c>
       <c r="B66" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A66,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A66,LEN('1. Elec Ref Grid'!A66)-FIND("-",'1. Elec Ref Grid'!A66))</f>
         <v>SE01</v>
       </c>
       <c r="C66" s="1" t="s">
@@ -18709,11 +18213,11 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A67,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A67,FIND("-",'1. Elec Ref Grid'!A67)-1)</f>
         <v>FI00</v>
       </c>
       <c r="B67" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A67,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A67,LEN('1. Elec Ref Grid'!A67)-FIND("-",'1. Elec Ref Grid'!A67))</f>
         <v>SE02</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -18729,11 +18233,11 @@
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A68,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A68,FIND("-",'1. Elec Ref Grid'!A68)-1)</f>
         <v>FI00</v>
       </c>
       <c r="B68" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A68,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A68,LEN('1. Elec Ref Grid'!A68)-FIND("-",'1. Elec Ref Grid'!A68))</f>
         <v>SE03</v>
       </c>
       <c r="C68" s="1" t="s">
@@ -18749,11 +18253,11 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A69,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A69,FIND("-",'1. Elec Ref Grid'!A69)-1)</f>
         <v>FR00</v>
       </c>
       <c r="B69" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A69,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A69,LEN('1. Elec Ref Grid'!A69)-FIND("-",'1. Elec Ref Grid'!A69))</f>
         <v>IE00</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -18769,11 +18273,11 @@
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A70,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A70,FIND("-",'1. Elec Ref Grid'!A70)-1)</f>
         <v>FR00</v>
       </c>
       <c r="B70" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A70,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A70,LEN('1. Elec Ref Grid'!A70)-FIND("-",'1. Elec Ref Grid'!A70))</f>
         <v>ITN1</v>
       </c>
       <c r="C70" s="1" t="s">
@@ -18789,11 +18293,11 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A71,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A71,FIND("-",'1. Elec Ref Grid'!A71)-1)</f>
         <v>FR00</v>
       </c>
       <c r="B71" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A71,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A71,LEN('1. Elec Ref Grid'!A71)-FIND("-",'1. Elec Ref Grid'!A71))</f>
         <v>LUF1</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -18809,11 +18313,11 @@
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A72,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A72,FIND("-",'1. Elec Ref Grid'!A72)-1)</f>
         <v>FR00</v>
       </c>
       <c r="B72" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A72,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A72,LEN('1. Elec Ref Grid'!A72)-FIND("-",'1. Elec Ref Grid'!A72))</f>
         <v>UK00</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -18829,11 +18333,11 @@
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A73,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A73,FIND("-",'1. Elec Ref Grid'!A73)-1)</f>
         <v>FR15</v>
       </c>
       <c r="B73" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A73,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A73,LEN('1. Elec Ref Grid'!A73)-FIND("-",'1. Elec Ref Grid'!A73))</f>
         <v>ITCO</v>
       </c>
       <c r="C73" s="1" t="s">
@@ -18849,11 +18353,11 @@
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A74,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A74,FIND("-",'1. Elec Ref Grid'!A74)-1)</f>
         <v>GR00</v>
       </c>
       <c r="B74" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A74,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A74,LEN('1. Elec Ref Grid'!A74)-FIND("-",'1. Elec Ref Grid'!A74))</f>
         <v>GR03</v>
       </c>
       <c r="C74" s="1" t="s">
@@ -18869,11 +18373,11 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A75,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A75,FIND("-",'1. Elec Ref Grid'!A75)-1)</f>
         <v>GR00</v>
       </c>
       <c r="B75" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A75,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A75,LEN('1. Elec Ref Grid'!A75)-FIND("-",'1. Elec Ref Grid'!A75))</f>
         <v>ITS1</v>
       </c>
       <c r="C75" s="1" t="s">
@@ -18889,11 +18393,11 @@
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A76,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A76,FIND("-",'1. Elec Ref Grid'!A76)-1)</f>
         <v>GR00</v>
       </c>
       <c r="B76" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A76,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A76,LEN('1. Elec Ref Grid'!A76)-FIND("-",'1. Elec Ref Grid'!A76))</f>
         <v>LY00</v>
       </c>
       <c r="C76" s="1" t="s">
@@ -18909,11 +18413,11 @@
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A77,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A77,FIND("-",'1. Elec Ref Grid'!A77)-1)</f>
         <v>GR00</v>
       </c>
       <c r="B77" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A77,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A77,LEN('1. Elec Ref Grid'!A77)-FIND("-",'1. Elec Ref Grid'!A77))</f>
         <v>MK00</v>
       </c>
       <c r="C77" s="1" t="s">
@@ -18929,11 +18433,11 @@
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A78,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A78,FIND("-",'1. Elec Ref Grid'!A78)-1)</f>
         <v>GR00</v>
       </c>
       <c r="B78" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A78,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A78,LEN('1. Elec Ref Grid'!A78)-FIND("-",'1. Elec Ref Grid'!A78))</f>
         <v>TR00</v>
       </c>
       <c r="C78" s="1" t="s">
@@ -18949,11 +18453,11 @@
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A79,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A79,FIND("-",'1. Elec Ref Grid'!A79)-1)</f>
         <v>GR03</v>
       </c>
       <c r="B79" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A79,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A79,LEN('1. Elec Ref Grid'!A79)-FIND("-",'1. Elec Ref Grid'!A79))</f>
         <v>LY00</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -18969,11 +18473,11 @@
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A80,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A80,FIND("-",'1. Elec Ref Grid'!A80)-1)</f>
         <v>HR00</v>
       </c>
       <c r="B80" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A80,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A80,LEN('1. Elec Ref Grid'!A80)-FIND("-",'1. Elec Ref Grid'!A80))</f>
         <v>HU00</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -18989,11 +18493,11 @@
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A81,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A81,FIND("-",'1. Elec Ref Grid'!A81)-1)</f>
         <v>HR00</v>
       </c>
       <c r="B81" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A81,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A81,LEN('1. Elec Ref Grid'!A81)-FIND("-",'1. Elec Ref Grid'!A81))</f>
         <v>RS00</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -19009,11 +18513,11 @@
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A82,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A82,FIND("-",'1. Elec Ref Grid'!A82)-1)</f>
         <v>HR00</v>
       </c>
       <c r="B82" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A82,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A82,LEN('1. Elec Ref Grid'!A82)-FIND("-",'1. Elec Ref Grid'!A82))</f>
         <v>SI00</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -19029,11 +18533,11 @@
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A83,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A83,FIND("-",'1. Elec Ref Grid'!A83)-1)</f>
         <v>HU00</v>
       </c>
       <c r="B83" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A83,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A83,LEN('1. Elec Ref Grid'!A83)-FIND("-",'1. Elec Ref Grid'!A83))</f>
         <v>RO00</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -19049,11 +18553,11 @@
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A84,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A84,FIND("-",'1. Elec Ref Grid'!A84)-1)</f>
         <v>HU00</v>
       </c>
       <c r="B84" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A84,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A84,LEN('1. Elec Ref Grid'!A84)-FIND("-",'1. Elec Ref Grid'!A84))</f>
         <v>RS00</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -19069,11 +18573,11 @@
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A85,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A85,FIND("-",'1. Elec Ref Grid'!A85)-1)</f>
         <v>HU00</v>
       </c>
       <c r="B85" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A85,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A85,LEN('1. Elec Ref Grid'!A85)-FIND("-",'1. Elec Ref Grid'!A85))</f>
         <v>SI00</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -19089,11 +18593,11 @@
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A86,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A86,FIND("-",'1. Elec Ref Grid'!A86)-1)</f>
         <v>HU00</v>
       </c>
       <c r="B86" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A86,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A86,LEN('1. Elec Ref Grid'!A86)-FIND("-",'1. Elec Ref Grid'!A86))</f>
         <v>SK00</v>
       </c>
       <c r="C86" s="1" t="s">
@@ -19109,11 +18613,11 @@
     </row>
     <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A87,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A87,FIND("-",'1. Elec Ref Grid'!A87)-1)</f>
         <v>HU00</v>
       </c>
       <c r="B87" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A87,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A87,LEN('1. Elec Ref Grid'!A87)-FIND("-",'1. Elec Ref Grid'!A87))</f>
         <v>UA01</v>
       </c>
       <c r="C87" s="1" t="s">
@@ -19129,11 +18633,11 @@
     </row>
     <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A88,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A88,FIND("-",'1. Elec Ref Grid'!A88)-1)</f>
         <v>IE00</v>
       </c>
       <c r="B88" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A88,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A88,LEN('1. Elec Ref Grid'!A88)-FIND("-",'1. Elec Ref Grid'!A88))</f>
         <v>UK00</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -19149,11 +18653,11 @@
     </row>
     <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A89,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A89,FIND("-",'1. Elec Ref Grid'!A89)-1)</f>
         <v>IE00</v>
       </c>
       <c r="B89" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A89,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A89,LEN('1. Elec Ref Grid'!A89)-FIND("-",'1. Elec Ref Grid'!A89))</f>
         <v>UKNI</v>
       </c>
       <c r="C89" s="1" t="s">
@@ -19169,11 +18673,11 @@
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A90,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A90,FIND("-",'1. Elec Ref Grid'!A90)-1)</f>
         <v>IL00</v>
       </c>
       <c r="B90" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A90,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A90,LEN('1. Elec Ref Grid'!A90)-FIND("-",'1. Elec Ref Grid'!A90))</f>
         <v>PS00</v>
       </c>
       <c r="C90" s="1" t="s">
@@ -19189,11 +18693,11 @@
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A91,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A91,FIND("-",'1. Elec Ref Grid'!A91)-1)</f>
         <v>IS00</v>
       </c>
       <c r="B91" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A91,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A91,LEN('1. Elec Ref Grid'!A91)-FIND("-",'1. Elec Ref Grid'!A91))</f>
         <v>UK00</v>
       </c>
       <c r="C91" s="1" t="s">
@@ -19209,11 +18713,11 @@
     </row>
     <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A92,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A92,FIND("-",'1. Elec Ref Grid'!A92)-1)</f>
         <v>ITCN</v>
       </c>
       <c r="B92" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A92,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A92,LEN('1. Elec Ref Grid'!A92)-FIND("-",'1. Elec Ref Grid'!A92))</f>
         <v>ITCO</v>
       </c>
       <c r="C92" s="1" t="s">
@@ -19229,11 +18733,11 @@
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A93,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A93,FIND("-",'1. Elec Ref Grid'!A93)-1)</f>
         <v>ITCN</v>
       </c>
       <c r="B93" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A93,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A93,LEN('1. Elec Ref Grid'!A93)-FIND("-",'1. Elec Ref Grid'!A93))</f>
         <v>ITCS</v>
       </c>
       <c r="C93" s="1" t="s">
@@ -19249,11 +18753,11 @@
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A94,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A94,FIND("-",'1. Elec Ref Grid'!A94)-1)</f>
         <v>ITCN</v>
       </c>
       <c r="B94" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A94,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A94,LEN('1. Elec Ref Grid'!A94)-FIND("-",'1. Elec Ref Grid'!A94))</f>
         <v>ITN1</v>
       </c>
       <c r="C94" s="1" t="s">
@@ -19269,11 +18773,11 @@
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A95,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A95,FIND("-",'1. Elec Ref Grid'!A95)-1)</f>
         <v>ITCO</v>
       </c>
       <c r="B95" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A95,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A95,LEN('1. Elec Ref Grid'!A95)-FIND("-",'1. Elec Ref Grid'!A95))</f>
         <v>ITSA</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -19289,11 +18793,11 @@
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A96,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A96,FIND("-",'1. Elec Ref Grid'!A96)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="B96" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A96,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A96,LEN('1. Elec Ref Grid'!A96)-FIND("-",'1. Elec Ref Grid'!A96))</f>
         <v>ITS1</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -19309,11 +18813,11 @@
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A97,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A97,FIND("-",'1. Elec Ref Grid'!A97)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="B97" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A97,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A97,LEN('1. Elec Ref Grid'!A97)-FIND("-",'1. Elec Ref Grid'!A97))</f>
         <v>ITSA</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -19329,12 +18833,12 @@
     </row>
     <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A98,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A98,FIND("-",'1. Elec Ref Grid'!A98)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="B98" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A98,4)</f>
-        <v>virt</v>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A98,LEN('1. Elec Ref Grid'!A98)-FIND("-",'1. Elec Ref Grid'!A98))</f>
+        <v>ITSIvirt</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>547</v>
@@ -19349,11 +18853,11 @@
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A99,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A99,FIND("-",'1. Elec Ref Grid'!A99)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="B99" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A99,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A99,LEN('1. Elec Ref Grid'!A99)-FIND("-",'1. Elec Ref Grid'!A99))</f>
         <v>ME00</v>
       </c>
       <c r="C99" s="1" t="s">
@@ -19369,11 +18873,11 @@
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A100,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A100,FIND("-",'1. Elec Ref Grid'!A100)-1)</f>
         <v>ITN1</v>
       </c>
       <c r="B100" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A100,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A100,LEN('1. Elec Ref Grid'!A100)-FIND("-",'1. Elec Ref Grid'!A100))</f>
         <v>SI00</v>
       </c>
       <c r="C100" s="1" t="s">
@@ -19389,11 +18893,11 @@
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A101,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A101,FIND("-",'1. Elec Ref Grid'!A101)-1)</f>
         <v>ITS1</v>
       </c>
       <c r="B101" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A101,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A101,LEN('1. Elec Ref Grid'!A101)-FIND("-",'1. Elec Ref Grid'!A101))</f>
         <v>ITCA</v>
       </c>
       <c r="C101" s="1" t="s">
@@ -19409,12 +18913,12 @@
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A102,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A102,FIND("-",'1. Elec Ref Grid'!A102)-1)</f>
         <v>ITSA</v>
       </c>
       <c r="B102" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A102,4)</f>
-        <v>virt</v>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A102,LEN('1. Elec Ref Grid'!A102)-FIND("-",'1. Elec Ref Grid'!A102))</f>
+        <v>ITSIvirt</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>547</v>
@@ -19429,11 +18933,11 @@
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A103,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A103,FIND("-",'1. Elec Ref Grid'!A103)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="B103" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A103,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A103,LEN('1. Elec Ref Grid'!A103)-FIND("-",'1. Elec Ref Grid'!A103))</f>
         <v>ITCA</v>
       </c>
       <c r="C103" s="1" t="s">
@@ -19449,12 +18953,12 @@
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A104,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A104,FIND("-",'1. Elec Ref Grid'!A104)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="B104" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A104,4)</f>
-        <v>virt</v>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A104,LEN('1. Elec Ref Grid'!A104)-FIND("-",'1. Elec Ref Grid'!A104))</f>
+        <v>ITSIvirt</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>547</v>
@@ -19469,11 +18973,11 @@
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A105,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A105,FIND("-",'1. Elec Ref Grid'!A105)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="B105" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A105,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A105,LEN('1. Elec Ref Grid'!A105)-FIND("-",'1. Elec Ref Grid'!A105))</f>
         <v>MT00</v>
       </c>
       <c r="C105" s="1" t="s">
@@ -19489,11 +18993,11 @@
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A106,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A106,FIND("-",'1. Elec Ref Grid'!A106)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="B106" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A106,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A106,LEN('1. Elec Ref Grid'!A106)-FIND("-",'1. Elec Ref Grid'!A106))</f>
         <v>TN00</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -19509,11 +19013,11 @@
     </row>
     <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A107,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A107,FIND("-",'1. Elec Ref Grid'!A107)-1)</f>
         <v>LT00</v>
       </c>
       <c r="B107" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A107,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A107,LEN('1. Elec Ref Grid'!A107)-FIND("-",'1. Elec Ref Grid'!A107))</f>
         <v>LV00</v>
       </c>
       <c r="C107" s="1" t="s">
@@ -19529,11 +19033,11 @@
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A108,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A108,FIND("-",'1. Elec Ref Grid'!A108)-1)</f>
         <v>LT00</v>
       </c>
       <c r="B108" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A108,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A108,LEN('1. Elec Ref Grid'!A108)-FIND("-",'1. Elec Ref Grid'!A108))</f>
         <v>PL00</v>
       </c>
       <c r="C108" s="1" t="s">
@@ -19549,11 +19053,11 @@
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A109,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A109,FIND("-",'1. Elec Ref Grid'!A109)-1)</f>
         <v>LT00</v>
       </c>
       <c r="B109" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A109,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A109,LEN('1. Elec Ref Grid'!A109)-FIND("-",'1. Elec Ref Grid'!A109))</f>
         <v>SE04</v>
       </c>
       <c r="C109" s="1" t="s">
@@ -19569,11 +19073,11 @@
     </row>
     <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A110,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A110,FIND("-",'1. Elec Ref Grid'!A110)-1)</f>
         <v>LY00</v>
       </c>
       <c r="B110" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A110,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A110,LEN('1. Elec Ref Grid'!A110)-FIND("-",'1. Elec Ref Grid'!A110))</f>
         <v>TN00</v>
       </c>
       <c r="C110" s="1" t="s">
@@ -19589,11 +19093,11 @@
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A111,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A111,FIND("-",'1. Elec Ref Grid'!A111)-1)</f>
         <v>ME00</v>
       </c>
       <c r="B111" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A111,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A111,LEN('1. Elec Ref Grid'!A111)-FIND("-",'1. Elec Ref Grid'!A111))</f>
         <v>RS00</v>
       </c>
       <c r="C111" s="1" t="s">
@@ -19609,11 +19113,11 @@
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A112,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A112,FIND("-",'1. Elec Ref Grid'!A112)-1)</f>
         <v>MK00</v>
       </c>
       <c r="B112" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A112,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A112,LEN('1. Elec Ref Grid'!A112)-FIND("-",'1. Elec Ref Grid'!A112))</f>
         <v>RS00</v>
       </c>
       <c r="C112" s="1" t="s">
@@ -19629,11 +19133,11 @@
     </row>
     <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A113,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A113,FIND("-",'1. Elec Ref Grid'!A113)-1)</f>
         <v>NL00</v>
       </c>
       <c r="B113" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A113,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A113,LEN('1. Elec Ref Grid'!A113)-FIND("-",'1. Elec Ref Grid'!A113))</f>
         <v>NOS0</v>
       </c>
       <c r="C113" s="1" t="s">
@@ -19649,11 +19153,11 @@
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A114,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A114,FIND("-",'1. Elec Ref Grid'!A114)-1)</f>
         <v>NL00</v>
       </c>
       <c r="B114" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A114,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A114,LEN('1. Elec Ref Grid'!A114)-FIND("-",'1. Elec Ref Grid'!A114))</f>
         <v>UK00</v>
       </c>
       <c r="C114" s="1" t="s">
@@ -19669,11 +19173,11 @@
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A115,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A115,FIND("-",'1. Elec Ref Grid'!A115)-1)</f>
         <v>NOM1</v>
       </c>
       <c r="B115" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A115,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A115,LEN('1. Elec Ref Grid'!A115)-FIND("-",'1. Elec Ref Grid'!A115))</f>
         <v>NON1</v>
       </c>
       <c r="C115" s="1" t="s">
@@ -19689,11 +19193,11 @@
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A116,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A116,FIND("-",'1. Elec Ref Grid'!A116)-1)</f>
         <v>NOM1</v>
       </c>
       <c r="B116" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A116,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A116,LEN('1. Elec Ref Grid'!A116)-FIND("-",'1. Elec Ref Grid'!A116))</f>
         <v>NOS0</v>
       </c>
       <c r="C116" s="1" t="s">
@@ -19709,11 +19213,11 @@
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A117,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A117,FIND("-",'1. Elec Ref Grid'!A117)-1)</f>
         <v>NOM1</v>
       </c>
       <c r="B117" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A117,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A117,LEN('1. Elec Ref Grid'!A117)-FIND("-",'1. Elec Ref Grid'!A117))</f>
         <v>SE02</v>
       </c>
       <c r="C117" s="1" t="s">
@@ -19729,11 +19233,11 @@
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A118,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A118,FIND("-",'1. Elec Ref Grid'!A118)-1)</f>
         <v>NON1</v>
       </c>
       <c r="B118" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A118,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A118,LEN('1. Elec Ref Grid'!A118)-FIND("-",'1. Elec Ref Grid'!A118))</f>
         <v>SE01</v>
       </c>
       <c r="C118" s="1" t="s">
@@ -19749,11 +19253,11 @@
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A119,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A119,FIND("-",'1. Elec Ref Grid'!A119)-1)</f>
         <v>NON1</v>
       </c>
       <c r="B119" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A119,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A119,LEN('1. Elec Ref Grid'!A119)-FIND("-",'1. Elec Ref Grid'!A119))</f>
         <v>SE02</v>
       </c>
       <c r="C119" s="1" t="s">
@@ -19769,11 +19273,11 @@
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A120,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A120,FIND("-",'1. Elec Ref Grid'!A120)-1)</f>
         <v>NOS0</v>
       </c>
       <c r="B120" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A120,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A120,LEN('1. Elec Ref Grid'!A120)-FIND("-",'1. Elec Ref Grid'!A120))</f>
         <v>SE03</v>
       </c>
       <c r="C120" s="1" t="s">
@@ -19789,11 +19293,11 @@
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A121,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A121,FIND("-",'1. Elec Ref Grid'!A121)-1)</f>
+        <v>PL00E</v>
       </c>
       <c r="B121" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A121,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A121,LEN('1. Elec Ref Grid'!A121)-FIND("-",'1. Elec Ref Grid'!A121))</f>
         <v>CZ00</v>
       </c>
       <c r="C121" s="1" t="s">
@@ -19809,11 +19313,11 @@
     </row>
     <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A122,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A122,FIND("-",'1. Elec Ref Grid'!A122)-1)</f>
+        <v>PL00E</v>
       </c>
       <c r="B122" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A122,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A122,LEN('1. Elec Ref Grid'!A122)-FIND("-",'1. Elec Ref Grid'!A122))</f>
         <v>DE00</v>
       </c>
       <c r="C122" s="1" t="s">
@@ -19829,11 +19333,11 @@
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A123,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A123,FIND("-",'1. Elec Ref Grid'!A123)-1)</f>
+        <v>PL00E</v>
       </c>
       <c r="B123" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A123,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A123,LEN('1. Elec Ref Grid'!A123)-FIND("-",'1. Elec Ref Grid'!A123))</f>
         <v>SK00</v>
       </c>
       <c r="C123" s="1" t="s">
@@ -19849,11 +19353,11 @@
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A124,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A124,FIND("-",'1. Elec Ref Grid'!A124)-1)</f>
+        <v>PL00I</v>
       </c>
       <c r="B124" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A124,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A124,LEN('1. Elec Ref Grid'!A124)-FIND("-",'1. Elec Ref Grid'!A124))</f>
         <v>PL00</v>
       </c>
       <c r="C124" s="1" t="s">
@@ -19869,12 +19373,12 @@
     </row>
     <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A125,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A125,FIND("-",'1. Elec Ref Grid'!A125)-1)</f>
         <v>PL00</v>
       </c>
       <c r="B125" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A125,4)</f>
-        <v>L00E</v>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A125,LEN('1. Elec Ref Grid'!A125)-FIND("-",'1. Elec Ref Grid'!A125))</f>
+        <v>PL00E</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>547</v>
@@ -19889,11 +19393,11 @@
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A126,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A126,FIND("-",'1. Elec Ref Grid'!A126)-1)</f>
         <v>PL00</v>
       </c>
       <c r="B126" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A126,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A126,LEN('1. Elec Ref Grid'!A126)-FIND("-",'1. Elec Ref Grid'!A126))</f>
         <v>SE04</v>
       </c>
       <c r="C126" s="1" t="s">
@@ -19909,11 +19413,11 @@
     </row>
     <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A127,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A127,FIND("-",'1. Elec Ref Grid'!A127)-1)</f>
         <v>RO00</v>
       </c>
       <c r="B127" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A127,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A127,LEN('1. Elec Ref Grid'!A127)-FIND("-",'1. Elec Ref Grid'!A127))</f>
         <v>RS00</v>
       </c>
       <c r="C127" s="1" t="s">
@@ -19929,11 +19433,11 @@
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A128,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A128,FIND("-",'1. Elec Ref Grid'!A128)-1)</f>
         <v>RO00</v>
       </c>
       <c r="B128" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A128,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A128,LEN('1. Elec Ref Grid'!A128)-FIND("-",'1. Elec Ref Grid'!A128))</f>
         <v>UA01</v>
       </c>
       <c r="C128" s="1" t="s">
@@ -19949,11 +19453,11 @@
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A129,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A129,FIND("-",'1. Elec Ref Grid'!A129)-1)</f>
         <v>SE01</v>
       </c>
       <c r="B129" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A129,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A129,LEN('1. Elec Ref Grid'!A129)-FIND("-",'1. Elec Ref Grid'!A129))</f>
         <v>SE02</v>
       </c>
       <c r="C129" s="1" t="s">
@@ -19969,11 +19473,11 @@
     </row>
     <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A130,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A130,FIND("-",'1. Elec Ref Grid'!A130)-1)</f>
         <v>SE02</v>
       </c>
       <c r="B130" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A130,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A130,LEN('1. Elec Ref Grid'!A130)-FIND("-",'1. Elec Ref Grid'!A130))</f>
         <v>SE03</v>
       </c>
       <c r="C130" s="1" t="s">
@@ -19989,11 +19493,11 @@
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A131,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A131,FIND("-",'1. Elec Ref Grid'!A131)-1)</f>
         <v>SE03</v>
       </c>
       <c r="B131" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A131,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A131,LEN('1. Elec Ref Grid'!A131)-FIND("-",'1. Elec Ref Grid'!A131))</f>
         <v>SE04</v>
       </c>
       <c r="C131" s="1" t="s">
@@ -20009,12 +19513,12 @@
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A132,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A132,FIND("-",'1. Elec Ref Grid'!A132)-1)</f>
         <v>SK00</v>
       </c>
       <c r="B132" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A132,4)</f>
-        <v>L00I</v>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A132,LEN('1. Elec Ref Grid'!A132)-FIND("-",'1. Elec Ref Grid'!A132))</f>
+        <v>PL00I</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>547</v>
@@ -20029,11 +19533,11 @@
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A133,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A133,FIND("-",'1. Elec Ref Grid'!A133)-1)</f>
         <v>SK00</v>
       </c>
       <c r="B133" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A133,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A133,LEN('1. Elec Ref Grid'!A133)-FIND("-",'1. Elec Ref Grid'!A133))</f>
         <v>UA01</v>
       </c>
       <c r="C133" s="1" t="s">
@@ -20049,11 +19553,11 @@
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A134,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A134,FIND("-",'1. Elec Ref Grid'!A134)-1)</f>
         <v>UK00</v>
       </c>
       <c r="B134" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A134,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A134,LEN('1. Elec Ref Grid'!A134)-FIND("-",'1. Elec Ref Grid'!A134))</f>
         <v>NOS0</v>
       </c>
       <c r="C134" s="1" t="s">
@@ -20069,11 +19573,11 @@
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A135,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A135,FIND("-",'1. Elec Ref Grid'!A135)-1)</f>
         <v>UK00</v>
       </c>
       <c r="B135" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A135,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A135,LEN('1. Elec Ref Grid'!A135)-FIND("-",'1. Elec Ref Grid'!A135))</f>
         <v>UKNI</v>
       </c>
       <c r="C135" s="1" t="s">
@@ -20089,11 +19593,11 @@
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A136,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A136,FIND("-",'1. Elec Ref Grid'!A136)-1)</f>
         <v>MD00</v>
       </c>
       <c r="B136" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A136,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A136,LEN('1. Elec Ref Grid'!A136)-FIND("-",'1. Elec Ref Grid'!A136))</f>
         <v>RO00</v>
       </c>
       <c r="C136" s="1" t="s">
@@ -20109,11 +19613,11 @@
     </row>
     <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A137,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A137,FIND("-",'1. Elec Ref Grid'!A137)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="B137" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A137,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A137,LEN('1. Elec Ref Grid'!A137)-FIND("-",'1. Elec Ref Grid'!A137))</f>
         <v>ITN1</v>
       </c>
       <c r="C137" s="1" t="s">
@@ -20129,11 +19633,11 @@
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A138,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A138,FIND("-",'1. Elec Ref Grid'!A138)-1)</f>
         <v>EG00</v>
       </c>
       <c r="B138" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A138,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A138,LEN('1. Elec Ref Grid'!A138)-FIND("-",'1. Elec Ref Grid'!A138))</f>
         <v>GR03</v>
       </c>
       <c r="C138" s="1" t="s">
@@ -20149,11 +19653,11 @@
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A139,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A139,FIND("-",'1. Elec Ref Grid'!A139)-1)</f>
         <v>HU00</v>
       </c>
       <c r="B139" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A139,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A139,LEN('1. Elec Ref Grid'!A139)-FIND("-",'1. Elec Ref Grid'!A139))</f>
         <v>UA00</v>
       </c>
       <c r="C139" s="1" t="s">
@@ -20169,11 +19673,11 @@
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A140,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A140,FIND("-",'1. Elec Ref Grid'!A140)-1)</f>
         <v>PL00</v>
       </c>
       <c r="B140" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A140,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A140,LEN('1. Elec Ref Grid'!A140)-FIND("-",'1. Elec Ref Grid'!A140))</f>
         <v>UA00</v>
       </c>
       <c r="C140" s="1" t="s">
@@ -20189,11 +19693,11 @@
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A141,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A141,FIND("-",'1. Elec Ref Grid'!A141)-1)</f>
         <v>RO00</v>
       </c>
       <c r="B141" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A141,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A141,LEN('1. Elec Ref Grid'!A141)-FIND("-",'1. Elec Ref Grid'!A141))</f>
         <v>UA00</v>
       </c>
       <c r="C141" s="1" t="s">
@@ -20209,11 +19713,11 @@
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A142,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A142,FIND("-",'1. Elec Ref Grid'!A142)-1)</f>
         <v>SK00</v>
       </c>
       <c r="B142" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A142,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A142,LEN('1. Elec Ref Grid'!A142)-FIND("-",'1. Elec Ref Grid'!A142))</f>
         <v>UA00</v>
       </c>
       <c r="C142" s="1" t="s">
@@ -20229,11 +19733,11 @@
     </row>
     <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A143,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A143,FIND("-",'1. Elec Ref Grid'!A143)-1)</f>
         <v>MD00</v>
       </c>
       <c r="B143" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A143,4)</f>
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A143,LEN('1. Elec Ref Grid'!A143)-FIND("-",'1. Elec Ref Grid'!A143))</f>
         <v>UA00</v>
       </c>
       <c r="C143" s="1" t="s">
@@ -20248,12 +19752,12 @@
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A2,4)</f>
+      <c r="A144" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A2,LEN('1. Elec Ref Grid'!A2)-FIND("-",'1. Elec Ref Grid'!A2))</f>
         <v>GR00</v>
       </c>
       <c r="B144" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A2,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A2,FIND("-",'1. Elec Ref Grid'!A2)-1)</f>
         <v>AL00</v>
       </c>
       <c r="C144" s="1" t="s">
@@ -20268,12 +19772,12 @@
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A3,4)</f>
+      <c r="A145" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A3,LEN('1. Elec Ref Grid'!A3)-FIND("-",'1. Elec Ref Grid'!A3))</f>
         <v>ME00</v>
       </c>
       <c r="B145" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A3,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A3,FIND("-",'1. Elec Ref Grid'!A3)-1)</f>
         <v>AL00</v>
       </c>
       <c r="C145" s="1" t="s">
@@ -20288,12 +19792,12 @@
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A4,4)</f>
+      <c r="A146" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A4,LEN('1. Elec Ref Grid'!A4)-FIND("-",'1. Elec Ref Grid'!A4))</f>
         <v>MK00</v>
       </c>
       <c r="B146" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A4,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A4,FIND("-",'1. Elec Ref Grid'!A4)-1)</f>
         <v>AL00</v>
       </c>
       <c r="C146" s="1" t="s">
@@ -20308,12 +19812,12 @@
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A5,4)</f>
+      <c r="A147" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A5,LEN('1. Elec Ref Grid'!A5)-FIND("-",'1. Elec Ref Grid'!A5))</f>
         <v>RS00</v>
       </c>
       <c r="B147" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A5,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A5,FIND("-",'1. Elec Ref Grid'!A5)-1)</f>
         <v>AL00</v>
       </c>
       <c r="C147" s="1" t="s">
@@ -20328,12 +19832,12 @@
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A6,4)</f>
+      <c r="A148" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A6,LEN('1. Elec Ref Grid'!A6)-FIND("-",'1. Elec Ref Grid'!A6))</f>
         <v>CH00</v>
       </c>
       <c r="B148" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A6,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A6,FIND("-",'1. Elec Ref Grid'!A6)-1)</f>
         <v>AT00</v>
       </c>
       <c r="C148" s="1" t="s">
@@ -20348,12 +19852,12 @@
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A7,4)</f>
+      <c r="A149" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A7,LEN('1. Elec Ref Grid'!A7)-FIND("-",'1. Elec Ref Grid'!A7))</f>
         <v>CZ00</v>
       </c>
       <c r="B149" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A7,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A7,FIND("-",'1. Elec Ref Grid'!A7)-1)</f>
         <v>AT00</v>
       </c>
       <c r="C149" s="1" t="s">
@@ -20368,12 +19872,12 @@
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A8,4)</f>
+      <c r="A150" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A8,LEN('1. Elec Ref Grid'!A8)-FIND("-",'1. Elec Ref Grid'!A8))</f>
         <v>DE00</v>
       </c>
       <c r="B150" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A8,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A8,FIND("-",'1. Elec Ref Grid'!A8)-1)</f>
         <v>AT00</v>
       </c>
       <c r="C150" s="1" t="s">
@@ -20388,12 +19892,12 @@
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A9,4)</f>
+      <c r="A151" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A9,LEN('1. Elec Ref Grid'!A9)-FIND("-",'1. Elec Ref Grid'!A9))</f>
         <v>HU00</v>
       </c>
       <c r="B151" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A9,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A9,FIND("-",'1. Elec Ref Grid'!A9)-1)</f>
         <v>AT00</v>
       </c>
       <c r="C151" s="1" t="s">
@@ -20408,12 +19912,12 @@
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A10,4)</f>
+      <c r="A152" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A10,LEN('1. Elec Ref Grid'!A10)-FIND("-",'1. Elec Ref Grid'!A10))</f>
         <v>ITN1</v>
       </c>
       <c r="B152" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A10,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A10,FIND("-",'1. Elec Ref Grid'!A10)-1)</f>
         <v>AT00</v>
       </c>
       <c r="C152" s="1" t="s">
@@ -20428,12 +19932,12 @@
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A11,4)</f>
+      <c r="A153" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A11,LEN('1. Elec Ref Grid'!A11)-FIND("-",'1. Elec Ref Grid'!A11))</f>
         <v>SI00</v>
       </c>
       <c r="B153" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A11,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A11,FIND("-",'1. Elec Ref Grid'!A11)-1)</f>
         <v>AT00</v>
       </c>
       <c r="C153" s="1" t="s">
@@ -20448,12 +19952,12 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A12,4)</f>
+      <c r="A154" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A12,LEN('1. Elec Ref Grid'!A12)-FIND("-",'1. Elec Ref Grid'!A12))</f>
         <v>SK00</v>
       </c>
       <c r="B154" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A12,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A12,FIND("-",'1. Elec Ref Grid'!A12)-1)</f>
         <v>AT00</v>
       </c>
       <c r="C154" s="1" t="s">
@@ -20468,12 +19972,12 @@
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A13,4)</f>
+      <c r="A155" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A13,LEN('1. Elec Ref Grid'!A13)-FIND("-",'1. Elec Ref Grid'!A13))</f>
         <v>HR00</v>
       </c>
       <c r="B155" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A13,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A13,FIND("-",'1. Elec Ref Grid'!A13)-1)</f>
         <v>BA00</v>
       </c>
       <c r="C155" s="1" t="s">
@@ -20488,12 +19992,12 @@
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A14,4)</f>
+      <c r="A156" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A14,LEN('1. Elec Ref Grid'!A14)-FIND("-",'1. Elec Ref Grid'!A14))</f>
         <v>ME00</v>
       </c>
       <c r="B156" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A14,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A14,FIND("-",'1. Elec Ref Grid'!A14)-1)</f>
         <v>BA00</v>
       </c>
       <c r="C156" s="1" t="s">
@@ -20508,12 +20012,12 @@
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A15,4)</f>
+      <c r="A157" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A15,LEN('1. Elec Ref Grid'!A15)-FIND("-",'1. Elec Ref Grid'!A15))</f>
         <v>RS00</v>
       </c>
       <c r="B157" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A15,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A15,FIND("-",'1. Elec Ref Grid'!A15)-1)</f>
         <v>BA00</v>
       </c>
       <c r="C157" s="1" t="s">
@@ -20528,12 +20032,12 @@
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A16,4)</f>
+      <c r="A158" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A16,LEN('1. Elec Ref Grid'!A16)-FIND("-",'1. Elec Ref Grid'!A16))</f>
         <v>DE00</v>
       </c>
       <c r="B158" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A16,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A16,FIND("-",'1. Elec Ref Grid'!A16)-1)</f>
         <v>BE00</v>
       </c>
       <c r="C158" s="1" t="s">
@@ -20548,12 +20052,12 @@
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A17,4)</f>
+      <c r="A159" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A17,LEN('1. Elec Ref Grid'!A17)-FIND("-",'1. Elec Ref Grid'!A17))</f>
         <v>FR00</v>
       </c>
       <c r="B159" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A17,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A17,FIND("-",'1. Elec Ref Grid'!A17)-1)</f>
         <v>BE00</v>
       </c>
       <c r="C159" s="1" t="s">
@@ -20568,12 +20072,12 @@
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A18,4)</f>
+      <c r="A160" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A18,LEN('1. Elec Ref Grid'!A18)-FIND("-",'1. Elec Ref Grid'!A18))</f>
         <v>LUB1</v>
       </c>
       <c r="B160" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A18,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A18,FIND("-",'1. Elec Ref Grid'!A18)-1)</f>
         <v>BE00</v>
       </c>
       <c r="C160" s="1" t="s">
@@ -20588,12 +20092,12 @@
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A19,4)</f>
+      <c r="A161" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A19,LEN('1. Elec Ref Grid'!A19)-FIND("-",'1. Elec Ref Grid'!A19))</f>
         <v>LUG1</v>
       </c>
       <c r="B161" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A19,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A19,FIND("-",'1. Elec Ref Grid'!A19)-1)</f>
         <v>BE00</v>
       </c>
       <c r="C161" s="1" t="s">
@@ -20608,12 +20112,12 @@
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A20,4)</f>
+      <c r="A162" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A20,LEN('1. Elec Ref Grid'!A20)-FIND("-",'1. Elec Ref Grid'!A20))</f>
         <v>NL00</v>
       </c>
       <c r="B162" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A20,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A20,FIND("-",'1. Elec Ref Grid'!A20)-1)</f>
         <v>BE00</v>
       </c>
       <c r="C162" s="1" t="s">
@@ -20628,12 +20132,12 @@
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A21,4)</f>
+      <c r="A163" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A21,LEN('1. Elec Ref Grid'!A21)-FIND("-",'1. Elec Ref Grid'!A21))</f>
         <v>UK00</v>
       </c>
       <c r="B163" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A21,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A21,FIND("-",'1. Elec Ref Grid'!A21)-1)</f>
         <v>BE00</v>
       </c>
       <c r="C163" s="1" t="s">
@@ -20648,12 +20152,12 @@
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A22,4)</f>
+      <c r="A164" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A22,LEN('1. Elec Ref Grid'!A22)-FIND("-",'1. Elec Ref Grid'!A22))</f>
         <v>GR00</v>
       </c>
       <c r="B164" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A22,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A22,FIND("-",'1. Elec Ref Grid'!A22)-1)</f>
         <v>BG00</v>
       </c>
       <c r="C164" s="1" t="s">
@@ -20668,12 +20172,12 @@
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A23,4)</f>
+      <c r="A165" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A23,LEN('1. Elec Ref Grid'!A23)-FIND("-",'1. Elec Ref Grid'!A23))</f>
         <v>MK00</v>
       </c>
       <c r="B165" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A23,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A23,FIND("-",'1. Elec Ref Grid'!A23)-1)</f>
         <v>BG00</v>
       </c>
       <c r="C165" s="1" t="s">
@@ -20688,12 +20192,12 @@
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A24,4)</f>
+      <c r="A166" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A24,LEN('1. Elec Ref Grid'!A24)-FIND("-",'1. Elec Ref Grid'!A24))</f>
         <v>RO00</v>
       </c>
       <c r="B166" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A24,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A24,FIND("-",'1. Elec Ref Grid'!A24)-1)</f>
         <v>BG00</v>
       </c>
       <c r="C166" s="1" t="s">
@@ -20708,12 +20212,12 @@
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A25,4)</f>
+      <c r="A167" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A25,LEN('1. Elec Ref Grid'!A25)-FIND("-",'1. Elec Ref Grid'!A25))</f>
         <v>RS00</v>
       </c>
       <c r="B167" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A25,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A25,FIND("-",'1. Elec Ref Grid'!A25)-1)</f>
         <v>BG00</v>
       </c>
       <c r="C167" s="1" t="s">
@@ -20728,12 +20232,12 @@
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A26,4)</f>
+      <c r="A168" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A26,LEN('1. Elec Ref Grid'!A26)-FIND("-",'1. Elec Ref Grid'!A26))</f>
         <v>TR00</v>
       </c>
       <c r="B168" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A26,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A26,FIND("-",'1. Elec Ref Grid'!A26)-1)</f>
         <v>BG00</v>
       </c>
       <c r="C168" s="1" t="s">
@@ -20748,12 +20252,12 @@
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A27,4)</f>
+      <c r="A169" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A27,LEN('1. Elec Ref Grid'!A27)-FIND("-",'1. Elec Ref Grid'!A27))</f>
         <v>DE00</v>
       </c>
       <c r="B169" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A27,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A27,FIND("-",'1. Elec Ref Grid'!A27)-1)</f>
         <v>CH00</v>
       </c>
       <c r="C169" s="1" t="s">
@@ -20768,12 +20272,12 @@
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A28,4)</f>
+      <c r="A170" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A28,LEN('1. Elec Ref Grid'!A28)-FIND("-",'1. Elec Ref Grid'!A28))</f>
         <v>FR00</v>
       </c>
       <c r="B170" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A28,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A28,FIND("-",'1. Elec Ref Grid'!A28)-1)</f>
         <v>CH00</v>
       </c>
       <c r="C170" s="1" t="s">
@@ -20788,12 +20292,12 @@
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A29,4)</f>
+      <c r="A171" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A29,LEN('1. Elec Ref Grid'!A29)-FIND("-",'1. Elec Ref Grid'!A29))</f>
         <v>ITN1</v>
       </c>
       <c r="B171" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A29,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A29,FIND("-",'1. Elec Ref Grid'!A29)-1)</f>
         <v>CH00</v>
       </c>
       <c r="C171" s="1" t="s">
@@ -20808,12 +20312,12 @@
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A30,4)</f>
+      <c r="A172" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A30,LEN('1. Elec Ref Grid'!A30)-FIND("-",'1. Elec Ref Grid'!A30))</f>
         <v>EG00</v>
       </c>
       <c r="B172" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A30,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A30,FIND("-",'1. Elec Ref Grid'!A30)-1)</f>
         <v>CY00</v>
       </c>
       <c r="C172" s="1" t="s">
@@ -20828,12 +20332,12 @@
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A31,4)</f>
+      <c r="A173" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A31,LEN('1. Elec Ref Grid'!A31)-FIND("-",'1. Elec Ref Grid'!A31))</f>
         <v>GR03</v>
       </c>
       <c r="B173" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A31,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A31,FIND("-",'1. Elec Ref Grid'!A31)-1)</f>
         <v>CY00</v>
       </c>
       <c r="C173" s="1" t="s">
@@ -20848,12 +20352,12 @@
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A32,4)</f>
+      <c r="A174" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A32,LEN('1. Elec Ref Grid'!A32)-FIND("-",'1. Elec Ref Grid'!A32))</f>
         <v>IL00</v>
       </c>
       <c r="B174" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A32,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A32,FIND("-",'1. Elec Ref Grid'!A32)-1)</f>
         <v>CY00</v>
       </c>
       <c r="C174" s="1" t="s">
@@ -20868,12 +20372,12 @@
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A33,4)</f>
+      <c r="A175" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A33,LEN('1. Elec Ref Grid'!A33)-FIND("-",'1. Elec Ref Grid'!A33))</f>
         <v>DE00</v>
       </c>
       <c r="B175" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A33,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A33,FIND("-",'1. Elec Ref Grid'!A33)-1)</f>
         <v>CZ00</v>
       </c>
       <c r="C175" s="1" t="s">
@@ -20888,12 +20392,12 @@
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A34,4)</f>
-        <v>L00I</v>
+      <c r="A176" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A34,LEN('1. Elec Ref Grid'!A34)-FIND("-",'1. Elec Ref Grid'!A34))</f>
+        <v>PL00I</v>
       </c>
       <c r="B176" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A34,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A34,FIND("-",'1. Elec Ref Grid'!A34)-1)</f>
         <v>CZ00</v>
       </c>
       <c r="C176" s="1" t="s">
@@ -20908,12 +20412,12 @@
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A35,4)</f>
+      <c r="A177" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A35,LEN('1. Elec Ref Grid'!A35)-FIND("-",'1. Elec Ref Grid'!A35))</f>
         <v>SK00</v>
       </c>
       <c r="B177" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A35,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A35,FIND("-",'1. Elec Ref Grid'!A35)-1)</f>
         <v>CZ00</v>
       </c>
       <c r="C177" s="1" t="s">
@@ -20928,12 +20432,12 @@
       </c>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A36,4)</f>
+      <c r="A178" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A36,LEN('1. Elec Ref Grid'!A36)-FIND("-",'1. Elec Ref Grid'!A36))</f>
         <v>DEKF</v>
       </c>
       <c r="B178" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A36,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A36,FIND("-",'1. Elec Ref Grid'!A36)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C178" s="1" t="s">
@@ -20948,12 +20452,12 @@
       </c>
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A37,4)</f>
+      <c r="A179" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A37,LEN('1. Elec Ref Grid'!A37)-FIND("-",'1. Elec Ref Grid'!A37))</f>
         <v>DKE1</v>
       </c>
       <c r="B179" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A37,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A37,FIND("-",'1. Elec Ref Grid'!A37)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C179" s="1" t="s">
@@ -20968,12 +20472,12 @@
       </c>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A38,4)</f>
+      <c r="A180" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A38,LEN('1. Elec Ref Grid'!A38)-FIND("-",'1. Elec Ref Grid'!A38))</f>
         <v>DKW1</v>
       </c>
       <c r="B180" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A38,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A38,FIND("-",'1. Elec Ref Grid'!A38)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C180" s="1" t="s">
@@ -20988,12 +20492,12 @@
       </c>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A39,4)</f>
+      <c r="A181" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A39,LEN('1. Elec Ref Grid'!A39)-FIND("-",'1. Elec Ref Grid'!A39))</f>
         <v>FR00</v>
       </c>
       <c r="B181" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A39,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A39,FIND("-",'1. Elec Ref Grid'!A39)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C181" s="1" t="s">
@@ -21008,12 +20512,12 @@
       </c>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A40,4)</f>
+      <c r="A182" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A40,LEN('1. Elec Ref Grid'!A40)-FIND("-",'1. Elec Ref Grid'!A40))</f>
         <v>LUG1</v>
       </c>
       <c r="B182" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A40,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A40,FIND("-",'1. Elec Ref Grid'!A40)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C182" s="1" t="s">
@@ -21028,12 +20532,12 @@
       </c>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A41,4)</f>
+      <c r="A183" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A41,LEN('1. Elec Ref Grid'!A41)-FIND("-",'1. Elec Ref Grid'!A41))</f>
         <v>LUV1</v>
       </c>
       <c r="B183" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A41,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A41,FIND("-",'1. Elec Ref Grid'!A41)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C183" s="1" t="s">
@@ -21048,12 +20552,12 @@
       </c>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A42,4)</f>
+      <c r="A184" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A42,LEN('1. Elec Ref Grid'!A42)-FIND("-",'1. Elec Ref Grid'!A42))</f>
         <v>NL00</v>
       </c>
       <c r="B184" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A42,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A42,FIND("-",'1. Elec Ref Grid'!A42)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C184" s="1" t="s">
@@ -21068,12 +20572,12 @@
       </c>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A43,4)</f>
+      <c r="A185" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A43,LEN('1. Elec Ref Grid'!A43)-FIND("-",'1. Elec Ref Grid'!A43))</f>
         <v>NOS0</v>
       </c>
       <c r="B185" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A43,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A43,FIND("-",'1. Elec Ref Grid'!A43)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C185" s="1" t="s">
@@ -21088,12 +20592,12 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A44,4)</f>
-        <v>L00I</v>
+      <c r="A186" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A44,LEN('1. Elec Ref Grid'!A44)-FIND("-",'1. Elec Ref Grid'!A44))</f>
+        <v>PL00I</v>
       </c>
       <c r="B186" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A44,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A44,FIND("-",'1. Elec Ref Grid'!A44)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C186" s="1" t="s">
@@ -21108,12 +20612,12 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A45,4)</f>
+      <c r="A187" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A45,LEN('1. Elec Ref Grid'!A45)-FIND("-",'1. Elec Ref Grid'!A45))</f>
         <v>SE04</v>
       </c>
       <c r="B187" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A45,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A45,FIND("-",'1. Elec Ref Grid'!A45)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C187" s="1" t="s">
@@ -21128,12 +20632,12 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A46,4)</f>
+      <c r="A188" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A46,LEN('1. Elec Ref Grid'!A46)-FIND("-",'1. Elec Ref Grid'!A46))</f>
         <v>UK00</v>
       </c>
       <c r="B188" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A46,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A46,FIND("-",'1. Elec Ref Grid'!A46)-1)</f>
         <v>DE00</v>
       </c>
       <c r="C188" s="1" t="s">
@@ -21148,12 +20652,12 @@
       </c>
     </row>
     <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A189" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A47,4)</f>
+      <c r="A189" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A47,LEN('1. Elec Ref Grid'!A47)-FIND("-",'1. Elec Ref Grid'!A47))</f>
         <v>DKKF</v>
       </c>
       <c r="B189" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A47,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A47,FIND("-",'1. Elec Ref Grid'!A47)-1)</f>
         <v>DEKF</v>
       </c>
       <c r="C189" s="1" t="s">
@@ -21168,12 +20672,12 @@
       </c>
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A48,4)</f>
+      <c r="A190" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A48,LEN('1. Elec Ref Grid'!A48)-FIND("-",'1. Elec Ref Grid'!A48))</f>
         <v>DKKF</v>
       </c>
       <c r="B190" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A48,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A48,FIND("-",'1. Elec Ref Grid'!A48)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="C190" s="1" t="s">
@@ -21188,12 +20692,12 @@
       </c>
     </row>
     <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A49,4)</f>
+      <c r="A191" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A49,LEN('1. Elec Ref Grid'!A49)-FIND("-",'1. Elec Ref Grid'!A49))</f>
         <v>DKW1</v>
       </c>
       <c r="B191" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A49,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A49,FIND("-",'1. Elec Ref Grid'!A49)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="C191" s="1" t="s">
@@ -21208,12 +20712,12 @@
       </c>
     </row>
     <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A50,4)</f>
+      <c r="A192" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A50,LEN('1. Elec Ref Grid'!A50)-FIND("-",'1. Elec Ref Grid'!A50))</f>
         <v>PL00</v>
       </c>
       <c r="B192" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A50,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A50,FIND("-",'1. Elec Ref Grid'!A50)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="C192" s="1" t="s">
@@ -21228,12 +20732,12 @@
       </c>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A51,4)</f>
+      <c r="A193" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A51,LEN('1. Elec Ref Grid'!A51)-FIND("-",'1. Elec Ref Grid'!A51))</f>
         <v>SE04</v>
       </c>
       <c r="B193" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A51,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A51,FIND("-",'1. Elec Ref Grid'!A51)-1)</f>
         <v>DKE1</v>
       </c>
       <c r="C193" s="1" t="s">
@@ -21248,12 +20752,12 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A52,4)</f>
+      <c r="A194" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A52,LEN('1. Elec Ref Grid'!A52)-FIND("-",'1. Elec Ref Grid'!A52))</f>
         <v>NL00</v>
       </c>
       <c r="B194" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A52,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A52,FIND("-",'1. Elec Ref Grid'!A52)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="C194" s="1" t="s">
@@ -21268,12 +20772,12 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A53,4)</f>
+      <c r="A195" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A53,LEN('1. Elec Ref Grid'!A53)-FIND("-",'1. Elec Ref Grid'!A53))</f>
         <v>NOS0</v>
       </c>
       <c r="B195" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A53,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A53,FIND("-",'1. Elec Ref Grid'!A53)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="C195" s="1" t="s">
@@ -21288,12 +20792,12 @@
       </c>
     </row>
     <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A54,4)</f>
+      <c r="A196" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A54,LEN('1. Elec Ref Grid'!A54)-FIND("-",'1. Elec Ref Grid'!A54))</f>
         <v>SE03</v>
       </c>
       <c r="B196" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A54,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A54,FIND("-",'1. Elec Ref Grid'!A54)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="C196" s="1" t="s">
@@ -21308,12 +20812,12 @@
       </c>
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A55,4)</f>
+      <c r="A197" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A55,LEN('1. Elec Ref Grid'!A55)-FIND("-",'1. Elec Ref Grid'!A55))</f>
         <v>UK00</v>
       </c>
       <c r="B197" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A55,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A55,FIND("-",'1. Elec Ref Grid'!A55)-1)</f>
         <v>DKW1</v>
       </c>
       <c r="C197" s="1" t="s">
@@ -21328,12 +20832,12 @@
       </c>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A56,4)</f>
+      <c r="A198" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A56,LEN('1. Elec Ref Grid'!A56)-FIND("-",'1. Elec Ref Grid'!A56))</f>
         <v>MA00</v>
       </c>
       <c r="B198" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A56,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A56,FIND("-",'1. Elec Ref Grid'!A56)-1)</f>
         <v>DZ00</v>
       </c>
       <c r="C198" s="1" t="s">
@@ -21348,12 +20852,12 @@
       </c>
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A57,4)</f>
+      <c r="A199" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A57,LEN('1. Elec Ref Grid'!A57)-FIND("-",'1. Elec Ref Grid'!A57))</f>
         <v>TN00</v>
       </c>
       <c r="B199" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A57,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A57,FIND("-",'1. Elec Ref Grid'!A57)-1)</f>
         <v>DZ00</v>
       </c>
       <c r="C199" s="1" t="s">
@@ -21368,12 +20872,12 @@
       </c>
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A58,4)</f>
+      <c r="A200" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A58,LEN('1. Elec Ref Grid'!A58)-FIND("-",'1. Elec Ref Grid'!A58))</f>
         <v>FI00</v>
       </c>
       <c r="B200" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A58,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A58,FIND("-",'1. Elec Ref Grid'!A58)-1)</f>
         <v>EE00</v>
       </c>
       <c r="C200" s="1" t="s">
@@ -21388,12 +20892,12 @@
       </c>
     </row>
     <row r="201" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A59,4)</f>
+      <c r="A201" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A59,LEN('1. Elec Ref Grid'!A59)-FIND("-",'1. Elec Ref Grid'!A59))</f>
         <v>LV00</v>
       </c>
       <c r="B201" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A59,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A59,FIND("-",'1. Elec Ref Grid'!A59)-1)</f>
         <v>EE00</v>
       </c>
       <c r="C201" s="1" t="s">
@@ -21408,12 +20912,12 @@
       </c>
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A60,4)</f>
+      <c r="A202" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A60,LEN('1. Elec Ref Grid'!A60)-FIND("-",'1. Elec Ref Grid'!A60))</f>
         <v>GR00</v>
       </c>
       <c r="B202" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A60,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A60,FIND("-",'1. Elec Ref Grid'!A60)-1)</f>
         <v>EG00</v>
       </c>
       <c r="C202" s="1" t="s">
@@ -21428,12 +20932,12 @@
       </c>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A203" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A61,4)</f>
+      <c r="A203" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A61,LEN('1. Elec Ref Grid'!A61)-FIND("-",'1. Elec Ref Grid'!A61))</f>
         <v>LY00</v>
       </c>
       <c r="B203" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A61,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A61,FIND("-",'1. Elec Ref Grid'!A61)-1)</f>
         <v>EG00</v>
       </c>
       <c r="C203" s="1" t="s">
@@ -21448,12 +20952,12 @@
       </c>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A62,4)</f>
+      <c r="A204" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A62,LEN('1. Elec Ref Grid'!A62)-FIND("-",'1. Elec Ref Grid'!A62))</f>
         <v>FR00</v>
       </c>
       <c r="B204" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A62,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A62,FIND("-",'1. Elec Ref Grid'!A62)-1)</f>
         <v>ES00</v>
       </c>
       <c r="C204" s="1" t="s">
@@ -21468,12 +20972,12 @@
       </c>
     </row>
     <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A205" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A63,4)</f>
+      <c r="A205" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A63,LEN('1. Elec Ref Grid'!A63)-FIND("-",'1. Elec Ref Grid'!A63))</f>
         <v>MA00</v>
       </c>
       <c r="B205" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A63,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A63,FIND("-",'1. Elec Ref Grid'!A63)-1)</f>
         <v>ES00</v>
       </c>
       <c r="C205" s="1" t="s">
@@ -21488,12 +20992,12 @@
       </c>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A206" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A64,4)</f>
+      <c r="A206" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A64,LEN('1. Elec Ref Grid'!A64)-FIND("-",'1. Elec Ref Grid'!A64))</f>
         <v>PT00</v>
       </c>
       <c r="B206" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A64,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A64,FIND("-",'1. Elec Ref Grid'!A64)-1)</f>
         <v>ES00</v>
       </c>
       <c r="C206" s="1" t="s">
@@ -21508,12 +21012,12 @@
       </c>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A65,4)</f>
+      <c r="A207" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A65,LEN('1. Elec Ref Grid'!A65)-FIND("-",'1. Elec Ref Grid'!A65))</f>
         <v>NON1</v>
       </c>
       <c r="B207" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A65,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A65,FIND("-",'1. Elec Ref Grid'!A65)-1)</f>
         <v>FI00</v>
       </c>
       <c r="C207" s="1" t="s">
@@ -21528,12 +21032,12 @@
       </c>
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A208" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A66,4)</f>
+      <c r="A208" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A66,LEN('1. Elec Ref Grid'!A66)-FIND("-",'1. Elec Ref Grid'!A66))</f>
         <v>SE01</v>
       </c>
       <c r="B208" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A66,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A66,FIND("-",'1. Elec Ref Grid'!A66)-1)</f>
         <v>FI00</v>
       </c>
       <c r="C208" s="1" t="s">
@@ -21548,12 +21052,12 @@
       </c>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A67,4)</f>
+      <c r="A209" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A67,LEN('1. Elec Ref Grid'!A67)-FIND("-",'1. Elec Ref Grid'!A67))</f>
         <v>SE02</v>
       </c>
       <c r="B209" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A67,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A67,FIND("-",'1. Elec Ref Grid'!A67)-1)</f>
         <v>FI00</v>
       </c>
       <c r="C209" s="1" t="s">
@@ -21568,12 +21072,12 @@
       </c>
     </row>
     <row r="210" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A210" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A68,4)</f>
+      <c r="A210" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A68,LEN('1. Elec Ref Grid'!A68)-FIND("-",'1. Elec Ref Grid'!A68))</f>
         <v>SE03</v>
       </c>
       <c r="B210" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A68,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A68,FIND("-",'1. Elec Ref Grid'!A68)-1)</f>
         <v>FI00</v>
       </c>
       <c r="C210" s="1" t="s">
@@ -21588,12 +21092,12 @@
       </c>
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A211" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A69,4)</f>
+      <c r="A211" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A69,LEN('1. Elec Ref Grid'!A69)-FIND("-",'1. Elec Ref Grid'!A69))</f>
         <v>IE00</v>
       </c>
       <c r="B211" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A69,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A69,FIND("-",'1. Elec Ref Grid'!A69)-1)</f>
         <v>FR00</v>
       </c>
       <c r="C211" s="1" t="s">
@@ -21608,12 +21112,12 @@
       </c>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A70,4)</f>
+      <c r="A212" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A70,LEN('1. Elec Ref Grid'!A70)-FIND("-",'1. Elec Ref Grid'!A70))</f>
         <v>ITN1</v>
       </c>
       <c r="B212" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A70,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A70,FIND("-",'1. Elec Ref Grid'!A70)-1)</f>
         <v>FR00</v>
       </c>
       <c r="C212" s="1" t="s">
@@ -21628,12 +21132,12 @@
       </c>
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A71,4)</f>
+      <c r="A213" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A71,LEN('1. Elec Ref Grid'!A71)-FIND("-",'1. Elec Ref Grid'!A71))</f>
         <v>LUF1</v>
       </c>
       <c r="B213" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A71,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A71,FIND("-",'1. Elec Ref Grid'!A71)-1)</f>
         <v>FR00</v>
       </c>
       <c r="C213" s="1" t="s">
@@ -21648,12 +21152,12 @@
       </c>
     </row>
     <row r="214" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A214" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A72,4)</f>
+      <c r="A214" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A72,LEN('1. Elec Ref Grid'!A72)-FIND("-",'1. Elec Ref Grid'!A72))</f>
         <v>UK00</v>
       </c>
       <c r="B214" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A72,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A72,FIND("-",'1. Elec Ref Grid'!A72)-1)</f>
         <v>FR00</v>
       </c>
       <c r="C214" s="1" t="s">
@@ -21668,12 +21172,12 @@
       </c>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A215" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A73,4)</f>
+      <c r="A215" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A73,LEN('1. Elec Ref Grid'!A73)-FIND("-",'1. Elec Ref Grid'!A73))</f>
         <v>ITCO</v>
       </c>
       <c r="B215" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A73,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A73,FIND("-",'1. Elec Ref Grid'!A73)-1)</f>
         <v>FR15</v>
       </c>
       <c r="C215" s="1" t="s">
@@ -21688,12 +21192,12 @@
       </c>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A74,4)</f>
+      <c r="A216" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A74,LEN('1. Elec Ref Grid'!A74)-FIND("-",'1. Elec Ref Grid'!A74))</f>
         <v>GR03</v>
       </c>
       <c r="B216" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A74,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A74,FIND("-",'1. Elec Ref Grid'!A74)-1)</f>
         <v>GR00</v>
       </c>
       <c r="C216" s="1" t="s">
@@ -21708,12 +21212,12 @@
       </c>
     </row>
     <row r="217" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A75,4)</f>
+      <c r="A217" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A75,LEN('1. Elec Ref Grid'!A75)-FIND("-",'1. Elec Ref Grid'!A75))</f>
         <v>ITS1</v>
       </c>
       <c r="B217" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A75,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A75,FIND("-",'1. Elec Ref Grid'!A75)-1)</f>
         <v>GR00</v>
       </c>
       <c r="C217" s="1" t="s">
@@ -21728,12 +21232,12 @@
       </c>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A76,4)</f>
+      <c r="A218" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A76,LEN('1. Elec Ref Grid'!A76)-FIND("-",'1. Elec Ref Grid'!A76))</f>
         <v>LY00</v>
       </c>
       <c r="B218" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A76,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A76,FIND("-",'1. Elec Ref Grid'!A76)-1)</f>
         <v>GR00</v>
       </c>
       <c r="C218" s="1" t="s">
@@ -21748,12 +21252,12 @@
       </c>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A219" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A77,4)</f>
+      <c r="A219" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A77,LEN('1. Elec Ref Grid'!A77)-FIND("-",'1. Elec Ref Grid'!A77))</f>
         <v>MK00</v>
       </c>
       <c r="B219" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A77,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A77,FIND("-",'1. Elec Ref Grid'!A77)-1)</f>
         <v>GR00</v>
       </c>
       <c r="C219" s="1" t="s">
@@ -21768,12 +21272,12 @@
       </c>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A78,4)</f>
+      <c r="A220" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A78,LEN('1. Elec Ref Grid'!A78)-FIND("-",'1. Elec Ref Grid'!A78))</f>
         <v>TR00</v>
       </c>
       <c r="B220" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A78,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A78,FIND("-",'1. Elec Ref Grid'!A78)-1)</f>
         <v>GR00</v>
       </c>
       <c r="C220" s="1" t="s">
@@ -21788,12 +21292,12 @@
       </c>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A79,4)</f>
+      <c r="A221" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A79,LEN('1. Elec Ref Grid'!A79)-FIND("-",'1. Elec Ref Grid'!A79))</f>
         <v>LY00</v>
       </c>
       <c r="B221" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A79,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A79,FIND("-",'1. Elec Ref Grid'!A79)-1)</f>
         <v>GR03</v>
       </c>
       <c r="C221" s="1" t="s">
@@ -21808,12 +21312,12 @@
       </c>
     </row>
     <row r="222" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A222" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A80,4)</f>
+      <c r="A222" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A80,LEN('1. Elec Ref Grid'!A80)-FIND("-",'1. Elec Ref Grid'!A80))</f>
         <v>HU00</v>
       </c>
       <c r="B222" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A80,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A80,FIND("-",'1. Elec Ref Grid'!A80)-1)</f>
         <v>HR00</v>
       </c>
       <c r="C222" s="1" t="s">
@@ -21828,12 +21332,12 @@
       </c>
     </row>
     <row r="223" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A81,4)</f>
+      <c r="A223" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A81,LEN('1. Elec Ref Grid'!A81)-FIND("-",'1. Elec Ref Grid'!A81))</f>
         <v>RS00</v>
       </c>
       <c r="B223" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A81,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A81,FIND("-",'1. Elec Ref Grid'!A81)-1)</f>
         <v>HR00</v>
       </c>
       <c r="C223" s="1" t="s">
@@ -21848,12 +21352,12 @@
       </c>
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A82,4)</f>
+      <c r="A224" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A82,LEN('1. Elec Ref Grid'!A82)-FIND("-",'1. Elec Ref Grid'!A82))</f>
         <v>SI00</v>
       </c>
       <c r="B224" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A82,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A82,FIND("-",'1. Elec Ref Grid'!A82)-1)</f>
         <v>HR00</v>
       </c>
       <c r="C224" s="1" t="s">
@@ -21868,12 +21372,12 @@
       </c>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A83,4)</f>
+      <c r="A225" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A83,LEN('1. Elec Ref Grid'!A83)-FIND("-",'1. Elec Ref Grid'!A83))</f>
         <v>RO00</v>
       </c>
       <c r="B225" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A83,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A83,FIND("-",'1. Elec Ref Grid'!A83)-1)</f>
         <v>HU00</v>
       </c>
       <c r="C225" s="1" t="s">
@@ -21888,12 +21392,12 @@
       </c>
     </row>
     <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A84,4)</f>
+      <c r="A226" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A84,LEN('1. Elec Ref Grid'!A84)-FIND("-",'1. Elec Ref Grid'!A84))</f>
         <v>RS00</v>
       </c>
       <c r="B226" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A84,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A84,FIND("-",'1. Elec Ref Grid'!A84)-1)</f>
         <v>HU00</v>
       </c>
       <c r="C226" s="1" t="s">
@@ -21908,12 +21412,12 @@
       </c>
     </row>
     <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A227" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A85,4)</f>
+      <c r="A227" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A85,LEN('1. Elec Ref Grid'!A85)-FIND("-",'1. Elec Ref Grid'!A85))</f>
         <v>SI00</v>
       </c>
       <c r="B227" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A85,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A85,FIND("-",'1. Elec Ref Grid'!A85)-1)</f>
         <v>HU00</v>
       </c>
       <c r="C227" s="1" t="s">
@@ -21928,12 +21432,12 @@
       </c>
     </row>
     <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A86,4)</f>
+      <c r="A228" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A86,LEN('1. Elec Ref Grid'!A86)-FIND("-",'1. Elec Ref Grid'!A86))</f>
         <v>SK00</v>
       </c>
       <c r="B228" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A86,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A86,FIND("-",'1. Elec Ref Grid'!A86)-1)</f>
         <v>HU00</v>
       </c>
       <c r="C228" s="1" t="s">
@@ -21948,12 +21452,12 @@
       </c>
     </row>
     <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A229" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A87,4)</f>
+      <c r="A229" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A87,LEN('1. Elec Ref Grid'!A87)-FIND("-",'1. Elec Ref Grid'!A87))</f>
         <v>UA01</v>
       </c>
       <c r="B229" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A87,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A87,FIND("-",'1. Elec Ref Grid'!A87)-1)</f>
         <v>HU00</v>
       </c>
       <c r="C229" s="1" t="s">
@@ -21968,12 +21472,12 @@
       </c>
     </row>
     <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A88,4)</f>
+      <c r="A230" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A88,LEN('1. Elec Ref Grid'!A88)-FIND("-",'1. Elec Ref Grid'!A88))</f>
         <v>UK00</v>
       </c>
       <c r="B230" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A88,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A88,FIND("-",'1. Elec Ref Grid'!A88)-1)</f>
         <v>IE00</v>
       </c>
       <c r="C230" s="1" t="s">
@@ -21988,12 +21492,12 @@
       </c>
     </row>
     <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A89,4)</f>
+      <c r="A231" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A89,LEN('1. Elec Ref Grid'!A89)-FIND("-",'1. Elec Ref Grid'!A89))</f>
         <v>UKNI</v>
       </c>
       <c r="B231" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A89,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A89,FIND("-",'1. Elec Ref Grid'!A89)-1)</f>
         <v>IE00</v>
       </c>
       <c r="C231" s="1" t="s">
@@ -22008,12 +21512,12 @@
       </c>
     </row>
     <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A232" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A90,4)</f>
+      <c r="A232" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A90,LEN('1. Elec Ref Grid'!A90)-FIND("-",'1. Elec Ref Grid'!A90))</f>
         <v>PS00</v>
       </c>
       <c r="B232" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A90,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A90,FIND("-",'1. Elec Ref Grid'!A90)-1)</f>
         <v>IL00</v>
       </c>
       <c r="C232" s="1" t="s">
@@ -22028,12 +21532,12 @@
       </c>
     </row>
     <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A91,4)</f>
+      <c r="A233" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A91,LEN('1. Elec Ref Grid'!A91)-FIND("-",'1. Elec Ref Grid'!A91))</f>
         <v>UK00</v>
       </c>
       <c r="B233" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A91,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A91,FIND("-",'1. Elec Ref Grid'!A91)-1)</f>
         <v>IS00</v>
       </c>
       <c r="C233" s="1" t="s">
@@ -22048,12 +21552,12 @@
       </c>
     </row>
     <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A92,4)</f>
+      <c r="A234" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A92,LEN('1. Elec Ref Grid'!A92)-FIND("-",'1. Elec Ref Grid'!A92))</f>
         <v>ITCO</v>
       </c>
       <c r="B234" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A92,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A92,FIND("-",'1. Elec Ref Grid'!A92)-1)</f>
         <v>ITCN</v>
       </c>
       <c r="C234" s="1" t="s">
@@ -22068,12 +21572,12 @@
       </c>
     </row>
     <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A93,4)</f>
+      <c r="A235" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A93,LEN('1. Elec Ref Grid'!A93)-FIND("-",'1. Elec Ref Grid'!A93))</f>
         <v>ITCS</v>
       </c>
       <c r="B235" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A93,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A93,FIND("-",'1. Elec Ref Grid'!A93)-1)</f>
         <v>ITCN</v>
       </c>
       <c r="C235" s="1" t="s">
@@ -22088,12 +21592,12 @@
       </c>
     </row>
     <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A236" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A94,4)</f>
+      <c r="A236" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A94,LEN('1. Elec Ref Grid'!A94)-FIND("-",'1. Elec Ref Grid'!A94))</f>
         <v>ITN1</v>
       </c>
       <c r="B236" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A94,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A94,FIND("-",'1. Elec Ref Grid'!A94)-1)</f>
         <v>ITCN</v>
       </c>
       <c r="C236" s="1" t="s">
@@ -22108,12 +21612,12 @@
       </c>
     </row>
     <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A95,4)</f>
+      <c r="A237" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A95,LEN('1. Elec Ref Grid'!A95)-FIND("-",'1. Elec Ref Grid'!A95))</f>
         <v>ITSA</v>
       </c>
       <c r="B237" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A95,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A95,FIND("-",'1. Elec Ref Grid'!A95)-1)</f>
         <v>ITCO</v>
       </c>
       <c r="C237" s="1" t="s">
@@ -22128,12 +21632,12 @@
       </c>
     </row>
     <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A238" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A96,4)</f>
+      <c r="A238" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A96,LEN('1. Elec Ref Grid'!A96)-FIND("-",'1. Elec Ref Grid'!A96))</f>
         <v>ITS1</v>
       </c>
       <c r="B238" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A96,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A96,FIND("-",'1. Elec Ref Grid'!A96)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="C238" s="1" t="s">
@@ -22148,12 +21652,12 @@
       </c>
     </row>
     <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A239" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A97,4)</f>
+      <c r="A239" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A97,LEN('1. Elec Ref Grid'!A97)-FIND("-",'1. Elec Ref Grid'!A97))</f>
         <v>ITSA</v>
       </c>
       <c r="B239" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A97,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A97,FIND("-",'1. Elec Ref Grid'!A97)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="C239" s="1" t="s">
@@ -22168,12 +21672,12 @@
       </c>
     </row>
     <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A98,4)</f>
-        <v>virt</v>
+      <c r="A240" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A98,LEN('1. Elec Ref Grid'!A98)-FIND("-",'1. Elec Ref Grid'!A98))</f>
+        <v>ITSIvirt</v>
       </c>
       <c r="B240" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A98,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A98,FIND("-",'1. Elec Ref Grid'!A98)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="C240" s="1" t="s">
@@ -22188,12 +21692,12 @@
       </c>
     </row>
     <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A241" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A99,4)</f>
+      <c r="A241" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A99,LEN('1. Elec Ref Grid'!A99)-FIND("-",'1. Elec Ref Grid'!A99))</f>
         <v>ME00</v>
       </c>
       <c r="B241" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A99,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A99,FIND("-",'1. Elec Ref Grid'!A99)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="C241" s="1" t="s">
@@ -22208,12 +21712,12 @@
       </c>
     </row>
     <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A100,4)</f>
+      <c r="A242" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A100,LEN('1. Elec Ref Grid'!A100)-FIND("-",'1. Elec Ref Grid'!A100))</f>
         <v>SI00</v>
       </c>
       <c r="B242" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A100,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A100,FIND("-",'1. Elec Ref Grid'!A100)-1)</f>
         <v>ITN1</v>
       </c>
       <c r="C242" s="1" t="s">
@@ -22228,12 +21732,12 @@
       </c>
     </row>
     <row r="243" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A243" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A101,4)</f>
+      <c r="A243" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A101,LEN('1. Elec Ref Grid'!A101)-FIND("-",'1. Elec Ref Grid'!A101))</f>
         <v>ITCA</v>
       </c>
       <c r="B243" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A101,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A101,FIND("-",'1. Elec Ref Grid'!A101)-1)</f>
         <v>ITS1</v>
       </c>
       <c r="C243" s="1" t="s">
@@ -22248,12 +21752,12 @@
       </c>
     </row>
     <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A244" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A102,4)</f>
-        <v>virt</v>
+      <c r="A244" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A102,LEN('1. Elec Ref Grid'!A102)-FIND("-",'1. Elec Ref Grid'!A102))</f>
+        <v>ITSIvirt</v>
       </c>
       <c r="B244" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A102,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A102,FIND("-",'1. Elec Ref Grid'!A102)-1)</f>
         <v>ITSA</v>
       </c>
       <c r="C244" s="1" t="s">
@@ -22268,12 +21772,12 @@
       </c>
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A245" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A103,4)</f>
+      <c r="A245" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A103,LEN('1. Elec Ref Grid'!A103)-FIND("-",'1. Elec Ref Grid'!A103))</f>
         <v>ITCA</v>
       </c>
       <c r="B245" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A103,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A103,FIND("-",'1. Elec Ref Grid'!A103)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="C245" s="1" t="s">
@@ -22288,12 +21792,12 @@
       </c>
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A104,4)</f>
-        <v>virt</v>
+      <c r="A246" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A104,LEN('1. Elec Ref Grid'!A104)-FIND("-",'1. Elec Ref Grid'!A104))</f>
+        <v>ITSIvirt</v>
       </c>
       <c r="B246" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A104,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A104,FIND("-",'1. Elec Ref Grid'!A104)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="C246" s="1" t="s">
@@ -22308,12 +21812,12 @@
       </c>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A247" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A105,4)</f>
+      <c r="A247" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A105,LEN('1. Elec Ref Grid'!A105)-FIND("-",'1. Elec Ref Grid'!A105))</f>
         <v>MT00</v>
       </c>
       <c r="B247" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A105,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A105,FIND("-",'1. Elec Ref Grid'!A105)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="C247" s="1" t="s">
@@ -22328,12 +21832,12 @@
       </c>
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A248" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A106,4)</f>
+      <c r="A248" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A106,LEN('1. Elec Ref Grid'!A106)-FIND("-",'1. Elec Ref Grid'!A106))</f>
         <v>TN00</v>
       </c>
       <c r="B248" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A106,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A106,FIND("-",'1. Elec Ref Grid'!A106)-1)</f>
         <v>ITSI</v>
       </c>
       <c r="C248" s="1" t="s">
@@ -22348,12 +21852,12 @@
       </c>
     </row>
     <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A107,4)</f>
+      <c r="A249" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A107,LEN('1. Elec Ref Grid'!A107)-FIND("-",'1. Elec Ref Grid'!A107))</f>
         <v>LV00</v>
       </c>
       <c r="B249" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A107,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A107,FIND("-",'1. Elec Ref Grid'!A107)-1)</f>
         <v>LT00</v>
       </c>
       <c r="C249" s="1" t="s">
@@ -22368,12 +21872,12 @@
       </c>
     </row>
     <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A250" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A108,4)</f>
+      <c r="A250" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A108,LEN('1. Elec Ref Grid'!A108)-FIND("-",'1. Elec Ref Grid'!A108))</f>
         <v>PL00</v>
       </c>
       <c r="B250" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A108,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A108,FIND("-",'1. Elec Ref Grid'!A108)-1)</f>
         <v>LT00</v>
       </c>
       <c r="C250" s="1" t="s">
@@ -22388,12 +21892,12 @@
       </c>
     </row>
     <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A109,4)</f>
+      <c r="A251" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A109,LEN('1. Elec Ref Grid'!A109)-FIND("-",'1. Elec Ref Grid'!A109))</f>
         <v>SE04</v>
       </c>
       <c r="B251" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A109,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A109,FIND("-",'1. Elec Ref Grid'!A109)-1)</f>
         <v>LT00</v>
       </c>
       <c r="C251" s="1" t="s">
@@ -22408,12 +21912,12 @@
       </c>
     </row>
     <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A110,4)</f>
+      <c r="A252" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A110,LEN('1. Elec Ref Grid'!A110)-FIND("-",'1. Elec Ref Grid'!A110))</f>
         <v>TN00</v>
       </c>
       <c r="B252" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A110,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A110,FIND("-",'1. Elec Ref Grid'!A110)-1)</f>
         <v>LY00</v>
       </c>
       <c r="C252" s="1" t="s">
@@ -22428,12 +21932,12 @@
       </c>
     </row>
     <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A253" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A111,4)</f>
+      <c r="A253" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A111,LEN('1. Elec Ref Grid'!A111)-FIND("-",'1. Elec Ref Grid'!A111))</f>
         <v>RS00</v>
       </c>
       <c r="B253" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A111,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A111,FIND("-",'1. Elec Ref Grid'!A111)-1)</f>
         <v>ME00</v>
       </c>
       <c r="C253" s="1" t="s">
@@ -22448,12 +21952,12 @@
       </c>
     </row>
     <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A254" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A112,4)</f>
+      <c r="A254" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A112,LEN('1. Elec Ref Grid'!A112)-FIND("-",'1. Elec Ref Grid'!A112))</f>
         <v>RS00</v>
       </c>
       <c r="B254" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A112,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A112,FIND("-",'1. Elec Ref Grid'!A112)-1)</f>
         <v>MK00</v>
       </c>
       <c r="C254" s="1" t="s">
@@ -22468,12 +21972,12 @@
       </c>
     </row>
     <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A255" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A113,4)</f>
+      <c r="A255" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A113,LEN('1. Elec Ref Grid'!A113)-FIND("-",'1. Elec Ref Grid'!A113))</f>
         <v>NOS0</v>
       </c>
       <c r="B255" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A113,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A113,FIND("-",'1. Elec Ref Grid'!A113)-1)</f>
         <v>NL00</v>
       </c>
       <c r="C255" s="1" t="s">
@@ -22488,12 +21992,12 @@
       </c>
     </row>
     <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A114,4)</f>
+      <c r="A256" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A114,LEN('1. Elec Ref Grid'!A114)-FIND("-",'1. Elec Ref Grid'!A114))</f>
         <v>UK00</v>
       </c>
       <c r="B256" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A114,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A114,FIND("-",'1. Elec Ref Grid'!A114)-1)</f>
         <v>NL00</v>
       </c>
       <c r="C256" s="1" t="s">
@@ -22508,12 +22012,12 @@
       </c>
     </row>
     <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A257" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A115,4)</f>
+      <c r="A257" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A115,LEN('1. Elec Ref Grid'!A115)-FIND("-",'1. Elec Ref Grid'!A115))</f>
         <v>NON1</v>
       </c>
       <c r="B257" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A115,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A115,FIND("-",'1. Elec Ref Grid'!A115)-1)</f>
         <v>NOM1</v>
       </c>
       <c r="C257" s="1" t="s">
@@ -22528,12 +22032,12 @@
       </c>
     </row>
     <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A116,4)</f>
+      <c r="A258" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A116,LEN('1. Elec Ref Grid'!A116)-FIND("-",'1. Elec Ref Grid'!A116))</f>
         <v>NOS0</v>
       </c>
       <c r="B258" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A116,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A116,FIND("-",'1. Elec Ref Grid'!A116)-1)</f>
         <v>NOM1</v>
       </c>
       <c r="C258" s="1" t="s">
@@ -22548,12 +22052,12 @@
       </c>
     </row>
     <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A259" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A117,4)</f>
+      <c r="A259" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A117,LEN('1. Elec Ref Grid'!A117)-FIND("-",'1. Elec Ref Grid'!A117))</f>
         <v>SE02</v>
       </c>
       <c r="B259" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A117,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A117,FIND("-",'1. Elec Ref Grid'!A117)-1)</f>
         <v>NOM1</v>
       </c>
       <c r="C259" s="1" t="s">
@@ -22568,12 +22072,12 @@
       </c>
     </row>
     <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A118,4)</f>
+      <c r="A260" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A118,LEN('1. Elec Ref Grid'!A118)-FIND("-",'1. Elec Ref Grid'!A118))</f>
         <v>SE01</v>
       </c>
       <c r="B260" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A118,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A118,FIND("-",'1. Elec Ref Grid'!A118)-1)</f>
         <v>NON1</v>
       </c>
       <c r="C260" s="1" t="s">
@@ -22588,12 +22092,12 @@
       </c>
     </row>
     <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A119,4)</f>
+      <c r="A261" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A119,LEN('1. Elec Ref Grid'!A119)-FIND("-",'1. Elec Ref Grid'!A119))</f>
         <v>SE02</v>
       </c>
       <c r="B261" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A119,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A119,FIND("-",'1. Elec Ref Grid'!A119)-1)</f>
         <v>NON1</v>
       </c>
       <c r="C261" s="1" t="s">
@@ -22608,12 +22112,12 @@
       </c>
     </row>
     <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A120,4)</f>
+      <c r="A262" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A120,LEN('1. Elec Ref Grid'!A120)-FIND("-",'1. Elec Ref Grid'!A120))</f>
         <v>SE03</v>
       </c>
       <c r="B262" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A120,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A120,FIND("-",'1. Elec Ref Grid'!A120)-1)</f>
         <v>NOS0</v>
       </c>
       <c r="C262" s="1" t="s">
@@ -22628,13 +22132,13 @@
       </c>
     </row>
     <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A121,4)</f>
+      <c r="A263" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A121,LEN('1. Elec Ref Grid'!A121)-FIND("-",'1. Elec Ref Grid'!A121))</f>
         <v>CZ00</v>
       </c>
       <c r="B263" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A121,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A121,FIND("-",'1. Elec Ref Grid'!A121)-1)</f>
+        <v>PL00E</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>547</v>
@@ -22648,13 +22152,13 @@
       </c>
     </row>
     <row r="264" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A264" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A122,4)</f>
+      <c r="A264" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A122,LEN('1. Elec Ref Grid'!A122)-FIND("-",'1. Elec Ref Grid'!A122))</f>
         <v>DE00</v>
       </c>
       <c r="B264" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A122,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A122,FIND("-",'1. Elec Ref Grid'!A122)-1)</f>
+        <v>PL00E</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>547</v>
@@ -22668,13 +22172,13 @@
       </c>
     </row>
     <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A265" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A123,4)</f>
+      <c r="A265" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A123,LEN('1. Elec Ref Grid'!A123)-FIND("-",'1. Elec Ref Grid'!A123))</f>
         <v>SK00</v>
       </c>
       <c r="B265" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A123,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A123,FIND("-",'1. Elec Ref Grid'!A123)-1)</f>
+        <v>PL00E</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>547</v>
@@ -22688,13 +22192,13 @@
       </c>
     </row>
     <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A266" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A124,4)</f>
+      <c r="A266" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A124,LEN('1. Elec Ref Grid'!A124)-FIND("-",'1. Elec Ref Grid'!A124))</f>
         <v>PL00</v>
       </c>
       <c r="B266" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A124,4)</f>
-        <v>PL00</v>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A124,FIND("-",'1. Elec Ref Grid'!A124)-1)</f>
+        <v>PL00I</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>547</v>
@@ -22708,12 +22212,12 @@
       </c>
     </row>
     <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A267" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A125,4)</f>
-        <v>L00E</v>
+      <c r="A267" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A125,LEN('1. Elec Ref Grid'!A125)-FIND("-",'1. Elec Ref Grid'!A125))</f>
+        <v>PL00E</v>
       </c>
       <c r="B267" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A125,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A125,FIND("-",'1. Elec Ref Grid'!A125)-1)</f>
         <v>PL00</v>
       </c>
       <c r="C267" s="1" t="s">
@@ -22728,12 +22232,12 @@
       </c>
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A126,4)</f>
+      <c r="A268" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A126,LEN('1. Elec Ref Grid'!A126)-FIND("-",'1. Elec Ref Grid'!A126))</f>
         <v>SE04</v>
       </c>
       <c r="B268" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A126,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A126,FIND("-",'1. Elec Ref Grid'!A126)-1)</f>
         <v>PL00</v>
       </c>
       <c r="C268" s="1" t="s">
@@ -22748,12 +22252,12 @@
       </c>
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A269" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A127,4)</f>
+      <c r="A269" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A127,LEN('1. Elec Ref Grid'!A127)-FIND("-",'1. Elec Ref Grid'!A127))</f>
         <v>RS00</v>
       </c>
       <c r="B269" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A127,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A127,FIND("-",'1. Elec Ref Grid'!A127)-1)</f>
         <v>RO00</v>
       </c>
       <c r="C269" s="1" t="s">
@@ -22768,12 +22272,12 @@
       </c>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A270" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A128,4)</f>
+      <c r="A270" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A128,LEN('1. Elec Ref Grid'!A128)-FIND("-",'1. Elec Ref Grid'!A128))</f>
         <v>UA01</v>
       </c>
       <c r="B270" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A128,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A128,FIND("-",'1. Elec Ref Grid'!A128)-1)</f>
         <v>RO00</v>
       </c>
       <c r="C270" s="1" t="s">
@@ -22788,12 +22292,12 @@
       </c>
     </row>
     <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A271" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A129,4)</f>
+      <c r="A271" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A129,LEN('1. Elec Ref Grid'!A129)-FIND("-",'1. Elec Ref Grid'!A129))</f>
         <v>SE02</v>
       </c>
       <c r="B271" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A129,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A129,FIND("-",'1. Elec Ref Grid'!A129)-1)</f>
         <v>SE01</v>
       </c>
       <c r="C271" s="1" t="s">
@@ -22808,12 +22312,12 @@
       </c>
     </row>
     <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A272" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A130,4)</f>
+      <c r="A272" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A130,LEN('1. Elec Ref Grid'!A130)-FIND("-",'1. Elec Ref Grid'!A130))</f>
         <v>SE03</v>
       </c>
       <c r="B272" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A130,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A130,FIND("-",'1. Elec Ref Grid'!A130)-1)</f>
         <v>SE02</v>
       </c>
       <c r="C272" s="1" t="s">
@@ -22828,12 +22332,12 @@
       </c>
     </row>
     <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A273" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A131,4)</f>
+      <c r="A273" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A131,LEN('1. Elec Ref Grid'!A131)-FIND("-",'1. Elec Ref Grid'!A131))</f>
         <v>SE04</v>
       </c>
       <c r="B273" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A131,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A131,FIND("-",'1. Elec Ref Grid'!A131)-1)</f>
         <v>SE03</v>
       </c>
       <c r="C273" s="1" t="s">
@@ -22848,12 +22352,12 @@
       </c>
     </row>
     <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A274" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A132,4)</f>
-        <v>L00I</v>
+      <c r="A274" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A132,LEN('1. Elec Ref Grid'!A132)-FIND("-",'1. Elec Ref Grid'!A132))</f>
+        <v>PL00I</v>
       </c>
       <c r="B274" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A132,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A132,FIND("-",'1. Elec Ref Grid'!A132)-1)</f>
         <v>SK00</v>
       </c>
       <c r="C274" s="1" t="s">
@@ -22868,12 +22372,12 @@
       </c>
     </row>
     <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A275" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A133,4)</f>
+      <c r="A275" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A133,LEN('1. Elec Ref Grid'!A133)-FIND("-",'1. Elec Ref Grid'!A133))</f>
         <v>UA01</v>
       </c>
       <c r="B275" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A133,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A133,FIND("-",'1. Elec Ref Grid'!A133)-1)</f>
         <v>SK00</v>
       </c>
       <c r="C275" s="1" t="s">
@@ -22888,12 +22392,12 @@
       </c>
     </row>
     <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A276" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A134,4)</f>
+      <c r="A276" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A134,LEN('1. Elec Ref Grid'!A134)-FIND("-",'1. Elec Ref Grid'!A134))</f>
         <v>NOS0</v>
       </c>
       <c r="B276" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A134,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A134,FIND("-",'1. Elec Ref Grid'!A134)-1)</f>
         <v>UK00</v>
       </c>
       <c r="C276" s="1" t="s">
@@ -22908,12 +22412,12 @@
       </c>
     </row>
     <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A277" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A135,4)</f>
+      <c r="A277" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A135,LEN('1. Elec Ref Grid'!A135)-FIND("-",'1. Elec Ref Grid'!A135))</f>
         <v>UKNI</v>
       </c>
       <c r="B277" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A135,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A135,FIND("-",'1. Elec Ref Grid'!A135)-1)</f>
         <v>UK00</v>
       </c>
       <c r="C277" s="1" t="s">
@@ -22928,12 +22432,12 @@
       </c>
     </row>
     <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A278" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A136,4)</f>
+      <c r="A278" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A136,LEN('1. Elec Ref Grid'!A136)-FIND("-",'1. Elec Ref Grid'!A136))</f>
         <v>RO00</v>
       </c>
       <c r="B278" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A136,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A136,FIND("-",'1. Elec Ref Grid'!A136)-1)</f>
         <v>MD00</v>
       </c>
       <c r="C278" s="1" t="s">
@@ -22948,12 +22452,12 @@
       </c>
     </row>
     <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A279" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A137,4)</f>
+      <c r="A279" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A137,LEN('1. Elec Ref Grid'!A137)-FIND("-",'1. Elec Ref Grid'!A137))</f>
         <v>ITN1</v>
       </c>
       <c r="B279" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A137,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A137,FIND("-",'1. Elec Ref Grid'!A137)-1)</f>
         <v>ITCS</v>
       </c>
       <c r="C279" s="1" t="s">
@@ -22968,12 +22472,12 @@
       </c>
     </row>
     <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A280" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A138,4)</f>
+      <c r="A280" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A138,LEN('1. Elec Ref Grid'!A138)-FIND("-",'1. Elec Ref Grid'!A138))</f>
         <v>GR03</v>
       </c>
       <c r="B280" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A138,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A138,FIND("-",'1. Elec Ref Grid'!A138)-1)</f>
         <v>EG00</v>
       </c>
       <c r="C280" s="1" t="s">
@@ -22988,12 +22492,12 @@
       </c>
     </row>
     <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A281" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A139,4)</f>
+      <c r="A281" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A139,LEN('1. Elec Ref Grid'!A139)-FIND("-",'1. Elec Ref Grid'!A139))</f>
         <v>UA00</v>
       </c>
       <c r="B281" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A139,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A139,FIND("-",'1. Elec Ref Grid'!A139)-1)</f>
         <v>HU00</v>
       </c>
       <c r="C281" s="1" t="s">
@@ -23008,12 +22512,12 @@
       </c>
     </row>
     <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A282" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A140,4)</f>
+      <c r="A282" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A140,LEN('1. Elec Ref Grid'!A140)-FIND("-",'1. Elec Ref Grid'!A140))</f>
         <v>UA00</v>
       </c>
       <c r="B282" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A140,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A140,FIND("-",'1. Elec Ref Grid'!A140)-1)</f>
         <v>PL00</v>
       </c>
       <c r="C282" s="1" t="s">
@@ -23028,12 +22532,12 @@
       </c>
     </row>
     <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A141,4)</f>
+      <c r="A283" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A141,LEN('1. Elec Ref Grid'!A141)-FIND("-",'1. Elec Ref Grid'!A141))</f>
         <v>UA00</v>
       </c>
       <c r="B283" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A141,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A141,FIND("-",'1. Elec Ref Grid'!A141)-1)</f>
         <v>RO00</v>
       </c>
       <c r="C283" s="1" t="s">
@@ -23048,12 +22552,12 @@
       </c>
     </row>
     <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A284" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A142,4)</f>
+      <c r="A284" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A142,LEN('1. Elec Ref Grid'!A142)-FIND("-",'1. Elec Ref Grid'!A142))</f>
         <v>UA00</v>
       </c>
       <c r="B284" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A142,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A142,FIND("-",'1. Elec Ref Grid'!A142)-1)</f>
         <v>SK00</v>
       </c>
       <c r="C284" s="1" t="s">
@@ -23068,12 +22572,12 @@
       </c>
     </row>
     <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A285" s="1" t="str">
-        <f aca="false">RIGHT('1. Elec Ref Grid'!A143,4)</f>
+      <c r="A285" s="16" t="str">
+        <f aca="false">RIGHT('1. Elec Ref Grid'!A143,LEN('1. Elec Ref Grid'!A143)-FIND("-",'1. Elec Ref Grid'!A143))</f>
         <v>UA00</v>
       </c>
       <c r="B285" s="12" t="str">
-        <f aca="false">LEFT('1. Elec Ref Grid'!A143,4)</f>
+        <f aca="false">LEFT('1. Elec Ref Grid'!A143,FIND("-",'1. Elec Ref Grid'!A143)-1)</f>
         <v>MD00</v>
       </c>
       <c r="C285" s="1" t="s">
@@ -23103,6 +22607,8 @@
       <c r="E286" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G286" s="12"/>
+      <c r="H286" s="12"/>
     </row>
     <row r="287" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="9" t="s">
@@ -23120,6 +22626,8 @@
       <c r="E287" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G287" s="12"/>
+      <c r="H287" s="12"/>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="9" t="s">
@@ -23137,6 +22645,8 @@
       <c r="E288" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G288" s="12"/>
+      <c r="H288" s="12"/>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="9" t="s">
@@ -23154,6 +22664,8 @@
       <c r="E289" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G289" s="12"/>
+      <c r="H289" s="12"/>
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="9" t="s">
@@ -23171,6 +22683,8 @@
       <c r="E290" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G290" s="12"/>
+      <c r="H290" s="12"/>
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="9" t="s">
@@ -23188,6 +22702,8 @@
       <c r="E291" s="9" t="n">
         <v>1400</v>
       </c>
+      <c r="G291" s="12"/>
+      <c r="H291" s="12"/>
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="9" t="s">
@@ -23205,6 +22721,8 @@
       <c r="E292" s="9" t="n">
         <v>200</v>
       </c>
+      <c r="G292" s="12"/>
+      <c r="H292" s="12"/>
     </row>
     <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="9" t="s">
@@ -23222,6 +22740,8 @@
       <c r="E293" s="9" t="n">
         <v>100</v>
       </c>
+      <c r="G293" s="12"/>
+      <c r="H293" s="12"/>
     </row>
     <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="9" t="s">
@@ -23239,6 +22759,8 @@
       <c r="E294" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G294" s="12"/>
+      <c r="H294" s="12"/>
     </row>
     <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="9" t="s">
@@ -23256,6 +22778,8 @@
       <c r="E295" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G295" s="12"/>
+      <c r="H295" s="12"/>
     </row>
     <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="9" t="s">
@@ -23273,6 +22797,8 @@
       <c r="E296" s="9" t="n">
         <v>1400</v>
       </c>
+      <c r="G296" s="12"/>
+      <c r="H296" s="12"/>
     </row>
     <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="9" t="s">
@@ -23290,6 +22816,8 @@
       <c r="E297" s="9" t="n">
         <v>1500</v>
       </c>
+      <c r="G297" s="12"/>
+      <c r="H297" s="12"/>
     </row>
     <row r="298" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="9" t="s">
@@ -23307,6 +22835,8 @@
       <c r="E298" s="9" t="n">
         <v>1500</v>
       </c>
+      <c r="G298" s="12"/>
+      <c r="H298" s="12"/>
     </row>
     <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="9" t="s">
@@ -23324,6 +22854,8 @@
       <c r="E299" s="9" t="n">
         <v>1250</v>
       </c>
+      <c r="G299" s="12"/>
+      <c r="H299" s="12"/>
     </row>
     <row r="300" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="9" t="s">
@@ -23341,6 +22873,8 @@
       <c r="E300" s="9" t="n">
         <v>950</v>
       </c>
+      <c r="G300" s="12"/>
+      <c r="H300" s="12"/>
     </row>
     <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="9" t="s">
@@ -23358,6 +22892,8 @@
       <c r="E301" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G301" s="12"/>
+      <c r="H301" s="12"/>
     </row>
     <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="9" t="s">
@@ -23375,6 +22911,8 @@
       <c r="E302" s="9" t="n">
         <v>998</v>
       </c>
+      <c r="G302" s="12"/>
+      <c r="H302" s="12"/>
     </row>
     <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="9" t="s">
@@ -23392,6 +22930,8 @@
       <c r="E303" s="9" t="n">
         <v>490</v>
       </c>
+      <c r="G303" s="12"/>
+      <c r="H303" s="12"/>
     </row>
     <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="9" t="s">
@@ -23409,6 +22949,8 @@
       <c r="E304" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G304" s="12"/>
+      <c r="H304" s="12"/>
     </row>
     <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="9" t="s">
@@ -23426,6 +22968,8 @@
       <c r="E305" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G305" s="12"/>
+      <c r="H305" s="12"/>
     </row>
     <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="9" t="s">
@@ -23443,6 +22987,8 @@
       <c r="E306" s="9" t="n">
         <v>1400</v>
       </c>
+      <c r="G306" s="12"/>
+      <c r="H306" s="12"/>
     </row>
     <row r="307" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="9" t="s">
@@ -23460,6 +23006,8 @@
       <c r="E307" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G307" s="12"/>
+      <c r="H307" s="12"/>
     </row>
     <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="9" t="s">
@@ -23477,6 +23025,8 @@
       <c r="E308" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G308" s="12"/>
+      <c r="H308" s="12"/>
     </row>
     <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="9" t="s">
@@ -23494,6 +23044,8 @@
       <c r="E309" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G309" s="12"/>
+      <c r="H309" s="12"/>
     </row>
     <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="9" t="s">
@@ -23511,6 +23063,8 @@
       <c r="E310" s="9" t="n">
         <v>800</v>
       </c>
+      <c r="G310" s="12"/>
+      <c r="H310" s="12"/>
     </row>
     <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="9" t="s">
@@ -23528,6 +23082,8 @@
       <c r="E311" s="9" t="n">
         <v>900</v>
       </c>
+      <c r="G311" s="12"/>
+      <c r="H311" s="12"/>
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="9" t="s">
@@ -23545,6 +23101,8 @@
       <c r="E312" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G312" s="12"/>
+      <c r="H312" s="12"/>
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="9" t="s">
@@ -23562,6 +23120,8 @@
       <c r="E313" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G313" s="12"/>
+      <c r="H313" s="12"/>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="9" t="s">
@@ -23579,6 +23139,8 @@
       <c r="E314" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G314" s="12"/>
+      <c r="H314" s="12"/>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="9" t="s">
@@ -23596,6 +23158,8 @@
       <c r="E315" s="9" t="n">
         <v>1410</v>
       </c>
+      <c r="G315" s="12"/>
+      <c r="H315" s="12"/>
     </row>
     <row r="316" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="9" t="s">
@@ -23613,6 +23177,8 @@
       <c r="E316" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G316" s="12"/>
+      <c r="H316" s="12"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="9" t="s">
@@ -23630,6 +23196,8 @@
       <c r="E317" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G317" s="12"/>
+      <c r="H317" s="12"/>
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="9" t="s">
@@ -23647,6 +23215,8 @@
       <c r="E318" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G318" s="12"/>
+      <c r="H318" s="12"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="9" t="s">
@@ -23664,6 +23234,8 @@
       <c r="E319" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G319" s="12"/>
+      <c r="H319" s="12"/>
     </row>
     <row r="320" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="9" t="s">
@@ -23681,6 +23253,8 @@
       <c r="E320" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G320" s="12"/>
+      <c r="H320" s="12"/>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="9" t="s">
@@ -23698,6 +23272,8 @@
       <c r="E321" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G321" s="12"/>
+      <c r="H321" s="12"/>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="9" t="s">
@@ -23715,6 +23291,8 @@
       <c r="E322" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G322" s="12"/>
+      <c r="H322" s="12"/>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="9" t="s">
@@ -23732,6 +23310,8 @@
       <c r="E323" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G323" s="12"/>
+      <c r="H323" s="12"/>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="9" t="s">
@@ -23749,6 +23329,8 @@
       <c r="E324" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G324" s="12"/>
+      <c r="H324" s="12"/>
     </row>
     <row r="325" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="9" t="s">
@@ -23766,6 +23348,8 @@
       <c r="E325" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G325" s="12"/>
+      <c r="H325" s="12"/>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="9" t="s">
@@ -23783,6 +23367,8 @@
       <c r="E326" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G326" s="12"/>
+      <c r="H326" s="12"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="9" t="s">
@@ -23800,6 +23386,8 @@
       <c r="E327" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G327" s="12"/>
+      <c r="H327" s="12"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="9" t="s">
@@ -23817,6 +23405,8 @@
       <c r="E328" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G328" s="12"/>
+      <c r="H328" s="12"/>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="9" t="s">
@@ -23834,6 +23424,8 @@
       <c r="E329" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G329" s="12"/>
+      <c r="H329" s="12"/>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="9" t="s">
@@ -23851,6 +23443,8 @@
       <c r="E330" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G330" s="12"/>
+      <c r="H330" s="12"/>
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="9" t="s">
@@ -23868,6 +23462,8 @@
       <c r="E331" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G331" s="12"/>
+      <c r="H331" s="12"/>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="9" t="s">
@@ -23885,6 +23481,8 @@
       <c r="E332" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G332" s="12"/>
+      <c r="H332" s="12"/>
     </row>
     <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="9" t="s">
@@ -23902,6 +23500,8 @@
       <c r="E333" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G333" s="12"/>
+      <c r="H333" s="12"/>
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="9" t="s">
@@ -23919,6 +23519,8 @@
       <c r="E334" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G334" s="12"/>
+      <c r="H334" s="12"/>
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="9" t="s">
@@ -23936,6 +23538,8 @@
       <c r="E335" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G335" s="12"/>
+      <c r="H335" s="12"/>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="9" t="s">
@@ -23953,6 +23557,8 @@
       <c r="E336" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G336" s="12"/>
+      <c r="H336" s="12"/>
     </row>
     <row r="337" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="9" t="s">
@@ -23970,6 +23576,8 @@
       <c r="E337" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G337" s="12"/>
+      <c r="H337" s="12"/>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="9" t="s">
@@ -23987,6 +23595,8 @@
       <c r="E338" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G338" s="12"/>
+      <c r="H338" s="12"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="9" t="s">
@@ -24004,6 +23614,8 @@
       <c r="E339" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G339" s="12"/>
+      <c r="H339" s="12"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="9" t="s">
@@ -24021,6 +23633,8 @@
       <c r="E340" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G340" s="12"/>
+      <c r="H340" s="12"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="9" t="s">
@@ -24038,6 +23652,8 @@
       <c r="E341" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G341" s="12"/>
+      <c r="H341" s="12"/>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="9" t="s">
@@ -24055,6 +23671,8 @@
       <c r="E342" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G342" s="12"/>
+      <c r="H342" s="12"/>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="9" t="s">
@@ -24072,6 +23690,8 @@
       <c r="E343" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G343" s="12"/>
+      <c r="H343" s="12"/>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="9" t="s">
@@ -24089,6 +23709,8 @@
       <c r="E344" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G344" s="12"/>
+      <c r="H344" s="12"/>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="9" t="s">
@@ -24106,6 +23728,8 @@
       <c r="E345" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G345" s="12"/>
+      <c r="H345" s="12"/>
     </row>
     <row r="346" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="9" t="s">
@@ -24123,6 +23747,8 @@
       <c r="E346" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G346" s="12"/>
+      <c r="H346" s="12"/>
     </row>
     <row r="347" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="9" t="s">
@@ -24140,6 +23766,8 @@
       <c r="E347" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G347" s="12"/>
+      <c r="H347" s="12"/>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="9" t="s">
@@ -24157,6 +23785,8 @@
       <c r="E348" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G348" s="12"/>
+      <c r="H348" s="12"/>
     </row>
     <row r="349" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="9" t="s">
@@ -24174,6 +23804,8 @@
       <c r="E349" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G349" s="12"/>
+      <c r="H349" s="12"/>
     </row>
     <row r="350" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="9" t="s">
@@ -24191,6 +23823,8 @@
       <c r="E350" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G350" s="12"/>
+      <c r="H350" s="12"/>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="9" t="s">
@@ -24208,6 +23842,8 @@
       <c r="E351" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G351" s="12"/>
+      <c r="H351" s="12"/>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="9" t="s">
@@ -24225,6 +23861,8 @@
       <c r="E352" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G352" s="12"/>
+      <c r="H352" s="12"/>
     </row>
     <row r="353" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="9" t="s">
@@ -24242,6 +23880,8 @@
       <c r="E353" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G353" s="12"/>
+      <c r="H353" s="12"/>
     </row>
     <row r="354" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="9" t="s">
@@ -24259,6 +23899,8 @@
       <c r="E354" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G354" s="12"/>
+      <c r="H354" s="12"/>
     </row>
     <row r="355" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="9" t="s">
@@ -24276,6 +23918,8 @@
       <c r="E355" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G355" s="12"/>
+      <c r="H355" s="12"/>
     </row>
     <row r="356" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="9" t="s">
@@ -24293,6 +23937,8 @@
       <c r="E356" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G356" s="12"/>
+      <c r="H356" s="12"/>
     </row>
     <row r="357" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="9" t="s">
@@ -24310,6 +23956,8 @@
       <c r="E357" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G357" s="12"/>
+      <c r="H357" s="12"/>
     </row>
     <row r="358" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="9" t="s">
@@ -24327,6 +23975,8 @@
       <c r="E358" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G358" s="12"/>
+      <c r="H358" s="12"/>
     </row>
     <row r="359" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="9" t="s">
@@ -24344,6 +23994,8 @@
       <c r="E359" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G359" s="12"/>
+      <c r="H359" s="12"/>
     </row>
     <row r="360" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="9" t="s">
@@ -24361,6 +24013,8 @@
       <c r="E360" s="9" t="n">
         <v>800</v>
       </c>
+      <c r="G360" s="12"/>
+      <c r="H360" s="12"/>
     </row>
     <row r="361" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="9" t="s">
@@ -24378,6 +24032,8 @@
       <c r="E361" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G361" s="12"/>
+      <c r="H361" s="12"/>
     </row>
     <row r="362" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="9" t="s">
@@ -24395,6 +24051,8 @@
       <c r="E362" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G362" s="12"/>
+      <c r="H362" s="12"/>
     </row>
     <row r="363" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="9" t="s">
@@ -24412,6 +24070,8 @@
       <c r="E363" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G363" s="12"/>
+      <c r="H363" s="12"/>
     </row>
     <row r="364" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="9" t="s">
@@ -24429,6 +24089,8 @@
       <c r="E364" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G364" s="12"/>
+      <c r="H364" s="12"/>
     </row>
     <row r="365" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="9" t="s">
@@ -24446,6 +24108,8 @@
       <c r="E365" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G365" s="12"/>
+      <c r="H365" s="12"/>
     </row>
     <row r="366" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="9" t="s">
@@ -24463,6 +24127,8 @@
       <c r="E366" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G366" s="12"/>
+      <c r="H366" s="12"/>
     </row>
     <row r="367" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="9" t="s">
@@ -24480,6 +24146,8 @@
       <c r="E367" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G367" s="12"/>
+      <c r="H367" s="12"/>
     </row>
     <row r="368" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="9" t="s">
@@ -24497,6 +24165,8 @@
       <c r="E368" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G368" s="12"/>
+      <c r="H368" s="12"/>
     </row>
     <row r="369" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="9" t="s">
@@ -24514,6 +24184,8 @@
       <c r="E369" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G369" s="12"/>
+      <c r="H369" s="12"/>
     </row>
     <row r="370" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="9" t="s">
@@ -24531,6 +24203,8 @@
       <c r="E370" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G370" s="12"/>
+      <c r="H370" s="12"/>
     </row>
     <row r="371" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="9" t="s">
@@ -24548,6 +24222,8 @@
       <c r="E371" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G371" s="12"/>
+      <c r="H371" s="12"/>
     </row>
     <row r="372" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="9" t="s">
@@ -24565,6 +24241,8 @@
       <c r="E372" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G372" s="12"/>
+      <c r="H372" s="12"/>
     </row>
     <row r="373" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="9" t="s">
@@ -24582,6 +24260,8 @@
       <c r="E373" s="9" t="n">
         <v>300</v>
       </c>
+      <c r="G373" s="12"/>
+      <c r="H373" s="12"/>
     </row>
     <row r="374" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="9" t="s">
@@ -24599,6 +24279,8 @@
       <c r="E374" s="9" t="n">
         <v>200</v>
       </c>
+      <c r="G374" s="12"/>
+      <c r="H374" s="12"/>
     </row>
     <row r="375" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="9" t="s">
@@ -24616,6 +24298,8 @@
       <c r="E375" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G375" s="12"/>
+      <c r="H375" s="12"/>
     </row>
     <row r="376" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="9" t="s">
@@ -24633,6 +24317,8 @@
       <c r="E376" s="9" t="n">
         <v>800</v>
       </c>
+      <c r="G376" s="12"/>
+      <c r="H376" s="12"/>
     </row>
     <row r="377" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="9" t="s">
@@ -24650,6 +24336,8 @@
       <c r="E377" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G377" s="12"/>
+      <c r="H377" s="12"/>
     </row>
     <row r="378" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="9" t="s">
@@ -24667,6 +24355,8 @@
       <c r="E378" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G378" s="12"/>
+      <c r="H378" s="12"/>
     </row>
     <row r="379" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="9" t="s">
@@ -24684,6 +24374,8 @@
       <c r="E379" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G379" s="12"/>
+      <c r="H379" s="12"/>
     </row>
     <row r="380" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="9" t="s">
@@ -24701,6 +24393,8 @@
       <c r="E380" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G380" s="12"/>
+      <c r="H380" s="12"/>
     </row>
     <row r="381" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="9" t="s">
@@ -24718,6 +24412,8 @@
       <c r="E381" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G381" s="12"/>
+      <c r="H381" s="12"/>
     </row>
     <row r="382" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="9" t="s">
@@ -24735,6 +24431,8 @@
       <c r="E382" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G382" s="12"/>
+      <c r="H382" s="12"/>
     </row>
     <row r="383" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="9" t="s">
@@ -24752,6 +24450,8 @@
       <c r="E383" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G383" s="12"/>
+      <c r="H383" s="12"/>
     </row>
     <row r="384" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="9" t="s">
@@ -24769,6 +24469,8 @@
       <c r="E384" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G384" s="12"/>
+      <c r="H384" s="12"/>
     </row>
     <row r="385" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="9" t="s">
@@ -24786,6 +24488,8 @@
       <c r="E385" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G385" s="12"/>
+      <c r="H385" s="12"/>
     </row>
     <row r="386" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="9" t="s">
@@ -24803,6 +24507,8 @@
       <c r="E386" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G386" s="12"/>
+      <c r="H386" s="12"/>
     </row>
     <row r="387" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="9" t="s">
@@ -24820,6 +24526,8 @@
       <c r="E387" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G387" s="12"/>
+      <c r="H387" s="12"/>
     </row>
     <row r="388" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="9" t="s">
@@ -24837,6 +24545,8 @@
       <c r="E388" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G388" s="12"/>
+      <c r="H388" s="12"/>
     </row>
     <row r="389" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="9" t="s">
@@ -24854,6 +24564,8 @@
       <c r="E389" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G389" s="12"/>
+      <c r="H389" s="12"/>
     </row>
     <row r="390" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="9" t="s">
@@ -24871,6 +24583,8 @@
       <c r="E390" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G390" s="12"/>
+      <c r="H390" s="12"/>
     </row>
     <row r="391" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="9" t="s">
@@ -24888,6 +24602,8 @@
       <c r="E391" s="9" t="n">
         <v>1400</v>
       </c>
+      <c r="G391" s="12"/>
+      <c r="H391" s="12"/>
     </row>
     <row r="392" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="9" t="s">
@@ -24905,6 +24621,8 @@
       <c r="E392" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="G392" s="12"/>
+      <c r="H392" s="12"/>
     </row>
     <row r="393" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="9" t="s">
@@ -24922,6 +24640,8 @@
       <c r="E393" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G393" s="12"/>
+      <c r="H393" s="12"/>
     </row>
     <row r="394" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="9" t="s">
@@ -24939,6 +24659,8 @@
       <c r="E394" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G394" s="12"/>
+      <c r="H394" s="12"/>
     </row>
     <row r="395" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="9" t="s">
@@ -24956,6 +24678,8 @@
       <c r="E395" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G395" s="12"/>
+      <c r="H395" s="12"/>
     </row>
     <row r="396" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="9" t="s">
@@ -24973,6 +24697,8 @@
       <c r="E396" s="9" t="n">
         <v>1400</v>
       </c>
+      <c r="G396" s="12"/>
+      <c r="H396" s="12"/>
     </row>
     <row r="397" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="9" t="s">
@@ -24990,6 +24716,8 @@
       <c r="E397" s="9" t="n">
         <v>1500</v>
       </c>
+      <c r="G397" s="12"/>
+      <c r="H397" s="12"/>
     </row>
     <row r="398" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="9" t="s">
@@ -25007,6 +24735,8 @@
       <c r="E398" s="9" t="n">
         <v>1500</v>
       </c>
+      <c r="G398" s="12"/>
+      <c r="H398" s="12"/>
     </row>
     <row r="399" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="9" t="s">
@@ -25024,6 +24754,8 @@
       <c r="E399" s="9" t="n">
         <v>1250</v>
       </c>
+      <c r="G399" s="12"/>
+      <c r="H399" s="12"/>
     </row>
     <row r="400" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="9" t="s">
@@ -25041,6 +24773,8 @@
       <c r="E400" s="9" t="n">
         <v>950</v>
       </c>
+      <c r="G400" s="12"/>
+      <c r="H400" s="12"/>
     </row>
     <row r="401" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="9" t="s">
@@ -25058,6 +24792,8 @@
       <c r="E401" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G401" s="12"/>
+      <c r="H401" s="12"/>
     </row>
     <row r="402" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="9" t="s">
@@ -25075,6 +24811,8 @@
       <c r="E402" s="9" t="n">
         <v>302</v>
       </c>
+      <c r="G402" s="12"/>
+      <c r="H402" s="12"/>
     </row>
     <row r="403" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="9" t="s">
@@ -25092,6 +24830,8 @@
       <c r="E403" s="9" t="n">
         <v>270</v>
       </c>
+      <c r="G403" s="12"/>
+      <c r="H403" s="12"/>
     </row>
     <row r="404" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="9" t="s">
@@ -25109,6 +24849,8 @@
       <c r="E404" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G404" s="12"/>
+      <c r="H404" s="12"/>
     </row>
     <row r="405" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="9" t="s">
@@ -25126,6 +24868,8 @@
       <c r="E405" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G405" s="12"/>
+      <c r="H405" s="12"/>
     </row>
     <row r="406" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="9" t="s">
@@ -25143,6 +24887,8 @@
       <c r="E406" s="9" t="n">
         <v>1400</v>
       </c>
+      <c r="G406" s="12"/>
+      <c r="H406" s="12"/>
     </row>
     <row r="407" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="9" t="s">
@@ -25160,6 +24906,8 @@
       <c r="E407" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G407" s="12"/>
+      <c r="H407" s="12"/>
     </row>
     <row r="408" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="9" t="s">
@@ -25177,6 +24925,8 @@
       <c r="E408" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G408" s="12"/>
+      <c r="H408" s="12"/>
     </row>
     <row r="409" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="9" t="s">
@@ -25194,6 +24944,8 @@
       <c r="E409" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G409" s="12"/>
+      <c r="H409" s="12"/>
     </row>
     <row r="410" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="9" t="s">
@@ -25211,6 +24963,8 @@
       <c r="E410" s="9" t="n">
         <v>800</v>
       </c>
+      <c r="G410" s="12"/>
+      <c r="H410" s="12"/>
     </row>
     <row r="411" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="9" t="s">
@@ -25228,6 +24982,8 @@
       <c r="E411" s="9" t="n">
         <v>800</v>
       </c>
+      <c r="G411" s="12"/>
+      <c r="H411" s="12"/>
     </row>
     <row r="412" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="9" t="s">
@@ -25245,6 +25001,8 @@
       <c r="E412" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G412" s="12"/>
+      <c r="H412" s="12"/>
     </row>
     <row r="413" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="9" t="s">
@@ -25262,6 +25020,8 @@
       <c r="E413" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G413" s="12"/>
+      <c r="H413" s="12"/>
     </row>
     <row r="414" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="9" t="s">
@@ -25279,6 +25039,8 @@
       <c r="E414" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G414" s="12"/>
+      <c r="H414" s="12"/>
     </row>
     <row r="415" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="9" t="s">
@@ -25296,6 +25058,8 @@
       <c r="E415" s="9" t="n">
         <v>740</v>
       </c>
+      <c r="G415" s="12"/>
+      <c r="H415" s="12"/>
     </row>
     <row r="416" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="9" t="s">
@@ -25313,6 +25077,8 @@
       <c r="E416" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G416" s="12"/>
+      <c r="H416" s="12"/>
     </row>
     <row r="417" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="9" t="s">
@@ -25330,6 +25096,8 @@
       <c r="E417" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G417" s="12"/>
+      <c r="H417" s="12"/>
     </row>
     <row r="418" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="9" t="s">
@@ -25347,6 +25115,8 @@
       <c r="E418" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G418" s="12"/>
+      <c r="H418" s="12"/>
     </row>
     <row r="419" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="9" t="s">
@@ -25364,6 +25134,8 @@
       <c r="E419" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G419" s="12"/>
+      <c r="H419" s="12"/>
     </row>
     <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="9" t="s">
@@ -25381,6 +25153,8 @@
       <c r="E420" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G420" s="12"/>
+      <c r="H420" s="12"/>
     </row>
     <row r="421" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="9" t="s">
@@ -25398,6 +25172,8 @@
       <c r="E421" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G421" s="12"/>
+      <c r="H421" s="12"/>
     </row>
     <row r="422" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="9" t="s">
@@ -25415,6 +25191,8 @@
       <c r="E422" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G422" s="12"/>
+      <c r="H422" s="12"/>
     </row>
     <row r="423" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="9" t="s">
@@ -25432,6 +25210,8 @@
       <c r="E423" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G423" s="12"/>
+      <c r="H423" s="12"/>
     </row>
     <row r="424" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="9" t="s">
@@ -25449,6 +25229,8 @@
       <c r="E424" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G424" s="12"/>
+      <c r="H424" s="12"/>
     </row>
     <row r="425" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="9" t="s">
@@ -25466,6 +25248,8 @@
       <c r="E425" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G425" s="12"/>
+      <c r="H425" s="12"/>
     </row>
     <row r="426" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="9" t="s">
@@ -25483,6 +25267,8 @@
       <c r="E426" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G426" s="12"/>
+      <c r="H426" s="12"/>
     </row>
     <row r="427" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="9" t="s">
@@ -25500,6 +25286,8 @@
       <c r="E427" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G427" s="12"/>
+      <c r="H427" s="12"/>
     </row>
     <row r="428" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="9" t="s">
@@ -25517,6 +25305,8 @@
       <c r="E428" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G428" s="12"/>
+      <c r="H428" s="12"/>
     </row>
     <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="9" t="s">
@@ -25534,6 +25324,8 @@
       <c r="E429" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G429" s="12"/>
+      <c r="H429" s="12"/>
     </row>
     <row r="430" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="9" t="s">
@@ -25551,6 +25343,8 @@
       <c r="E430" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G430" s="12"/>
+      <c r="H430" s="12"/>
     </row>
     <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="9" t="s">
@@ -25568,6 +25362,8 @@
       <c r="E431" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G431" s="12"/>
+      <c r="H431" s="12"/>
     </row>
     <row r="432" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="9" t="s">
@@ -25585,6 +25381,8 @@
       <c r="E432" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G432" s="12"/>
+      <c r="H432" s="12"/>
     </row>
     <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="9" t="s">
@@ -25602,6 +25400,8 @@
       <c r="E433" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G433" s="12"/>
+      <c r="H433" s="12"/>
     </row>
     <row r="434" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="9" t="s">
@@ -25619,6 +25419,8 @@
       <c r="E434" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G434" s="12"/>
+      <c r="H434" s="12"/>
     </row>
     <row r="435" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="9" t="s">
@@ -25636,6 +25438,8 @@
       <c r="E435" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G435" s="12"/>
+      <c r="H435" s="12"/>
     </row>
     <row r="436" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="9" t="s">
@@ -25653,6 +25457,8 @@
       <c r="E436" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G436" s="12"/>
+      <c r="H436" s="12"/>
     </row>
     <row r="437" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="9" t="s">
@@ -25670,6 +25476,8 @@
       <c r="E437" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G437" s="12"/>
+      <c r="H437" s="12"/>
     </row>
     <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="9" t="s">
@@ -25687,6 +25495,8 @@
       <c r="E438" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G438" s="12"/>
+      <c r="H438" s="12"/>
     </row>
     <row r="439" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="9" t="s">
@@ -25704,6 +25514,8 @@
       <c r="E439" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G439" s="12"/>
+      <c r="H439" s="12"/>
     </row>
     <row r="440" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="9" t="s">
@@ -25721,6 +25533,8 @@
       <c r="E440" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G440" s="12"/>
+      <c r="H440" s="12"/>
     </row>
     <row r="441" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="9" t="s">
@@ -25738,6 +25552,8 @@
       <c r="E441" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G441" s="12"/>
+      <c r="H441" s="12"/>
     </row>
     <row r="442" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="9" t="s">
@@ -25755,6 +25571,8 @@
       <c r="E442" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G442" s="12"/>
+      <c r="H442" s="12"/>
     </row>
     <row r="443" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="9" t="s">
@@ -25772,6 +25590,8 @@
       <c r="E443" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G443" s="12"/>
+      <c r="H443" s="12"/>
     </row>
     <row r="444" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="9" t="s">
@@ -25789,6 +25609,8 @@
       <c r="E444" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G444" s="12"/>
+      <c r="H444" s="12"/>
     </row>
     <row r="445" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="9" t="s">
@@ -25806,6 +25628,8 @@
       <c r="E445" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G445" s="12"/>
+      <c r="H445" s="12"/>
     </row>
     <row r="446" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="9" t="s">
@@ -25823,6 +25647,8 @@
       <c r="E446" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G446" s="12"/>
+      <c r="H446" s="12"/>
     </row>
     <row r="447" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="9" t="s">
@@ -25840,6 +25666,8 @@
       <c r="E447" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G447" s="12"/>
+      <c r="H447" s="12"/>
     </row>
     <row r="448" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="9" t="s">
@@ -25857,6 +25685,8 @@
       <c r="E448" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G448" s="12"/>
+      <c r="H448" s="12"/>
     </row>
     <row r="449" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="9" t="s">
@@ -25874,6 +25704,8 @@
       <c r="E449" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G449" s="12"/>
+      <c r="H449" s="12"/>
     </row>
     <row r="450" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="9" t="s">
@@ -25891,6 +25723,8 @@
       <c r="E450" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G450" s="12"/>
+      <c r="H450" s="12"/>
     </row>
     <row r="451" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="9" t="s">
@@ -25908,6 +25742,8 @@
       <c r="E451" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G451" s="12"/>
+      <c r="H451" s="12"/>
     </row>
     <row r="452" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="9" t="s">
@@ -25925,6 +25761,8 @@
       <c r="E452" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G452" s="12"/>
+      <c r="H452" s="12"/>
     </row>
     <row r="453" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="9" t="s">
@@ -25942,6 +25780,8 @@
       <c r="E453" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G453" s="12"/>
+      <c r="H453" s="12"/>
     </row>
     <row r="454" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="9" t="s">
@@ -25959,6 +25799,8 @@
       <c r="E454" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G454" s="12"/>
+      <c r="H454" s="12"/>
     </row>
     <row r="455" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="9" t="s">
@@ -25976,6 +25818,8 @@
       <c r="E455" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G455" s="12"/>
+      <c r="H455" s="12"/>
     </row>
     <row r="456" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="9" t="s">
@@ -25993,6 +25837,8 @@
       <c r="E456" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G456" s="12"/>
+      <c r="H456" s="12"/>
     </row>
     <row r="457" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="9" t="s">
@@ -26010,6 +25856,8 @@
       <c r="E457" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G457" s="12"/>
+      <c r="H457" s="12"/>
     </row>
     <row r="458" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="9" t="s">
@@ -26027,6 +25875,8 @@
       <c r="E458" s="9" t="n">
         <v>700</v>
       </c>
+      <c r="G458" s="12"/>
+      <c r="H458" s="12"/>
     </row>
     <row r="459" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="9" t="s">
@@ -26044,6 +25894,8 @@
       <c r="E459" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G459" s="12"/>
+      <c r="H459" s="12"/>
     </row>
     <row r="460" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="9" t="s">
@@ -26061,6 +25913,8 @@
       <c r="E460" s="9" t="n">
         <v>800</v>
       </c>
+      <c r="G460" s="12"/>
+      <c r="H460" s="12"/>
     </row>
     <row r="461" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="9" t="s">
@@ -26078,6 +25932,8 @@
       <c r="E461" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G461" s="12"/>
+      <c r="H461" s="12"/>
     </row>
     <row r="462" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="9" t="s">
@@ -26095,6 +25951,8 @@
       <c r="E462" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G462" s="12"/>
+      <c r="H462" s="12"/>
     </row>
     <row r="463" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="9" t="s">
@@ -26112,6 +25970,8 @@
       <c r="E463" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G463" s="12"/>
+      <c r="H463" s="12"/>
     </row>
     <row r="464" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="9" t="s">
@@ -26129,6 +25989,8 @@
       <c r="E464" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G464" s="12"/>
+      <c r="H464" s="12"/>
     </row>
     <row r="465" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="9" t="s">
@@ -26146,6 +26008,8 @@
       <c r="E465" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G465" s="12"/>
+      <c r="H465" s="12"/>
     </row>
     <row r="466" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="9" t="s">
@@ -26163,6 +26027,8 @@
       <c r="E466" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G466" s="12"/>
+      <c r="H466" s="12"/>
     </row>
     <row r="467" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="9" t="s">
@@ -26180,6 +26046,8 @@
       <c r="E467" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G467" s="12"/>
+      <c r="H467" s="12"/>
     </row>
     <row r="468" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="9" t="s">
@@ -26197,6 +26065,8 @@
       <c r="E468" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G468" s="12"/>
+      <c r="H468" s="12"/>
     </row>
     <row r="469" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="9" t="s">
@@ -26214,6 +26084,8 @@
       <c r="E469" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G469" s="12"/>
+      <c r="H469" s="12"/>
     </row>
     <row r="470" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="9" t="s">
@@ -26231,6 +26103,8 @@
       <c r="E470" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G470" s="12"/>
+      <c r="H470" s="12"/>
     </row>
     <row r="471" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="9" t="s">
@@ -26248,6 +26122,8 @@
       <c r="E471" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G471" s="12"/>
+      <c r="H471" s="12"/>
     </row>
     <row r="472" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="9" t="s">
@@ -26265,6 +26141,8 @@
       <c r="E472" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G472" s="12"/>
+      <c r="H472" s="12"/>
     </row>
     <row r="473" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="9" t="s">
@@ -26282,6 +26160,8 @@
       <c r="E473" s="9" t="n">
         <v>300</v>
       </c>
+      <c r="G473" s="12"/>
+      <c r="H473" s="12"/>
     </row>
     <row r="474" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="9" t="s">
@@ -26299,6 +26179,8 @@
       <c r="E474" s="9" t="n">
         <v>200</v>
       </c>
+      <c r="G474" s="12"/>
+      <c r="H474" s="12"/>
     </row>
     <row r="475" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="9" t="s">
@@ -26316,6 +26198,8 @@
       <c r="E475" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G475" s="12"/>
+      <c r="H475" s="12"/>
     </row>
     <row r="476" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="9" t="s">
@@ -26333,6 +26217,8 @@
       <c r="E476" s="9" t="n">
         <v>0</v>
       </c>
+      <c r="G476" s="12"/>
+      <c r="H476" s="12"/>
     </row>
     <row r="477" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="9" t="s">
@@ -26350,6 +26236,8 @@
       <c r="E477" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G477" s="12"/>
+      <c r="H477" s="12"/>
     </row>
     <row r="478" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="9" t="s">
@@ -26367,6 +26255,8 @@
       <c r="E478" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G478" s="12"/>
+      <c r="H478" s="12"/>
     </row>
     <row r="479" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="9" t="s">
@@ -26384,6 +26274,8 @@
       <c r="E479" s="9" t="n">
         <v>500</v>
       </c>
+      <c r="G479" s="12"/>
+      <c r="H479" s="12"/>
     </row>
     <row r="480" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="9" t="s">
@@ -26401,6 +26293,8 @@
       <c r="E480" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G480" s="12"/>
+      <c r="H480" s="12"/>
     </row>
     <row r="481" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="9" t="s">
@@ -26418,6 +26312,8 @@
       <c r="E481" s="9" t="n">
         <v>600</v>
       </c>
+      <c r="G481" s="12"/>
+      <c r="H481" s="12"/>
     </row>
     <row r="482" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="9" t="s">
@@ -26435,6 +26331,8 @@
       <c r="E482" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G482" s="12"/>
+      <c r="H482" s="12"/>
     </row>
     <row r="483" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="9" t="s">
@@ -26452,6 +26350,8 @@
       <c r="E483" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G483" s="12"/>
+      <c r="H483" s="12"/>
     </row>
     <row r="484" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="9" t="s">
@@ -26469,6 +26369,8 @@
       <c r="E484" s="9" t="n">
         <v>2000</v>
       </c>
+      <c r="G484" s="12"/>
+      <c r="H484" s="12"/>
     </row>
     <row r="485" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="9" t="s">
@@ -26486,6 +26388,8 @@
       <c r="E485" s="9" t="n">
         <v>1000</v>
       </c>
+      <c r="G485" s="12"/>
+      <c r="H485" s="12"/>
     </row>
     <row r="486" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
